--- a/data/indicadores/03_03_02_06_tub.xlsx
+++ b/data/indicadores/03_03_02_06_tub.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pasantia\atlas ods 2025\Bases de datos indicadores\Finales y con codigo correcto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02D27E6-83FB-44D8-A8E7-01FC5159E652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B66F891-C4C2-47C9-B485-8B2E75C4DAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{6CE7CDF0-8068-4477-9E8B-5D0A7DC34D21}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="6" xr2:uid="{6CE7CDF0-8068-4477-9E8B-5D0A7DC34D21}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos originales" sheetId="1" r:id="rId1"/>
@@ -2643,10 +2643,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 3">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD514861-3410-4710-9026-97CBB0CF6612}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04CA5BDF-D5B2-4587-BE8D-2D79254A2606}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -40588,2603 +40588,2603 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="29">
-        <v>10101</v>
+        <v>20606</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>8</v>
+        <v>406</v>
       </c>
       <c r="C2" s="36">
-        <v>40.324561058351229</v>
+        <v>340.05362762099861</v>
       </c>
       <c r="D2" s="36">
-        <v>40.533333333333331</v>
+        <v>433.36666666666662</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="29">
-        <v>10102</v>
+        <v>21801</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>9</v>
+        <v>454</v>
       </c>
       <c r="C3" s="36">
-        <v>29.783315852938625</v>
+        <v>235.00507397318805</v>
       </c>
       <c r="D3" s="36">
-        <v>44</v>
+        <v>4.6000000000000005</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="29">
-        <v>10103</v>
+        <v>70403</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>364</v>
+        <v>276</v>
       </c>
       <c r="C4" s="36">
-        <v>48.775773236622378</v>
+        <v>172.92490044349407</v>
       </c>
       <c r="D4" s="36">
-        <v>35.93333333333333</v>
+        <v>154.1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="29">
-        <v>10201</v>
+        <v>31602</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>365</v>
+        <v>506</v>
       </c>
       <c r="C5" s="36">
-        <v>51.206758404444997</v>
+        <v>158.91903299949041</v>
       </c>
       <c r="D5" s="36">
-        <v>20.8</v>
+        <v>216.06666666666669</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="29">
-        <v>10202</v>
+        <v>31202</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>12</v>
+        <v>490</v>
       </c>
       <c r="C6" s="36">
-        <v>11.385580207384047</v>
+        <v>147.50306807283704</v>
       </c>
       <c r="D6" s="36">
-        <v>24</v>
+        <v>26.333333333333332</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="29">
-        <v>10301</v>
+        <v>31003</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>366</v>
+        <v>488</v>
       </c>
       <c r="C7" s="36">
-        <v>45.763307149606995</v>
+        <v>144.65881280349035</v>
       </c>
       <c r="D7" s="36">
-        <v>61.199999999999996</v>
+        <v>121.13333333333333</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="29">
-        <v>10302</v>
+        <v>10901</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C8" s="36">
-        <v>59.678832075248657</v>
+        <v>143.41619153142292</v>
       </c>
       <c r="D8" s="36">
-        <v>63.166666666666664</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="29">
-        <v>10303</v>
+        <v>22002</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>367</v>
+        <v>460</v>
       </c>
       <c r="C9" s="36">
-        <v>25.048509503259666</v>
+        <v>138.32329700374385</v>
       </c>
       <c r="D9" s="36">
-        <v>29.833333333333332</v>
+        <v>132.5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="29">
-        <v>10304</v>
+        <v>31206</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>16</v>
+        <v>494</v>
       </c>
       <c r="C10" s="36">
-        <v>16.105698736805746</v>
+        <v>138.27360567027779</v>
       </c>
       <c r="D10" s="36">
-        <v>53.966666666666661</v>
+        <v>199.20000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="29">
-        <v>10401</v>
+        <v>22001</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>17</v>
+        <v>459</v>
       </c>
       <c r="C11" s="36">
-        <v>13.924720239973412</v>
+        <v>127.76093843136567</v>
       </c>
       <c r="D11" s="36">
-        <v>35.9</v>
+        <v>316.83333333333331</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="29">
-        <v>10402</v>
+        <v>21105</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>18</v>
+        <v>433</v>
       </c>
       <c r="C12" s="36">
-        <v>26.769607654622558</v>
+        <v>125.18333198810002</v>
       </c>
       <c r="D12" s="36">
-        <v>44.300000000000004</v>
+        <v>185.33333333333334</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="29">
-        <v>10403</v>
+        <v>20601</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>19</v>
+        <v>401</v>
       </c>
       <c r="C13" s="36">
-        <v>55.45445770337367</v>
+        <v>122.01798038806714</v>
       </c>
       <c r="D13" s="36">
-        <v>16.5</v>
+        <v>103.86666666666667</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="29">
-        <v>10404</v>
+        <v>60202</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>368</v>
+        <v>254</v>
       </c>
       <c r="C14" s="36">
-        <v>0</v>
+        <v>121.11815105301442</v>
       </c>
       <c r="D14" s="36">
-        <v>0</v>
+        <v>84.233333333333334</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="29">
-        <v>10405</v>
+        <v>71502</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>21</v>
+        <v>318</v>
       </c>
       <c r="C15" s="36">
-        <v>0</v>
+        <v>117.96212307504335</v>
       </c>
       <c r="D15" s="36">
-        <v>8.3333333333333339</v>
+        <v>69.600000000000009</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="29">
-        <v>10501</v>
+        <v>20607</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>22</v>
+        <v>407</v>
       </c>
       <c r="C16" s="36">
-        <v>39.499227389632154</v>
+        <v>117.62798904714681</v>
       </c>
       <c r="D16" s="36">
-        <v>37.033333333333331</v>
+        <v>218.83333333333334</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="29">
-        <v>10502</v>
+        <v>21402</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>369</v>
+        <v>446</v>
       </c>
       <c r="C17" s="36">
-        <v>19.916942113738454</v>
+        <v>117.16708649386037</v>
       </c>
       <c r="D17" s="36">
-        <v>20.233333333333334</v>
+        <v>161.30000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="29">
-        <v>10601</v>
+        <v>71402</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>24</v>
+        <v>315</v>
       </c>
       <c r="C18" s="36">
-        <v>49.552111627744544</v>
+        <v>116.98729902377134</v>
       </c>
       <c r="D18" s="36">
-        <v>47.866666666666667</v>
+        <v>125.66666666666667</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="29">
-        <v>10602</v>
+        <v>31204</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>370</v>
+        <v>492</v>
       </c>
       <c r="C19" s="36">
-        <v>14.357462895918644</v>
+        <v>114.6362595260177</v>
       </c>
       <c r="D19" s="36">
-        <v>62.9</v>
+        <v>206.73333333333335</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="29">
-        <v>10701</v>
+        <v>21101</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>26</v>
+        <v>429</v>
       </c>
       <c r="C20" s="36">
-        <v>50.573331570098809</v>
+        <v>114.13715864761683</v>
       </c>
       <c r="D20" s="36">
-        <v>34.333333333333336</v>
+        <v>194.26666666666665</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="29">
-        <v>10702</v>
+        <v>60303</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>27</v>
+        <v>527</v>
       </c>
       <c r="C21" s="36">
-        <v>46.449535089086275</v>
+        <v>113.49326857512436</v>
       </c>
       <c r="D21" s="36">
-        <v>56.233333333333327</v>
+        <v>75.899999999999991</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="29">
-        <v>10703</v>
+        <v>71001</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c r="C22" s="36">
-        <v>63.846394167045865</v>
+        <v>112.69900946488991</v>
       </c>
       <c r="D22" s="36">
-        <v>63.466666666666661</v>
+        <v>226.9666666666667</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="29">
-        <v>10704</v>
+        <v>70201</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>29</v>
+        <v>269</v>
       </c>
       <c r="C23" s="36">
-        <v>94.029606321871725</v>
+        <v>109.22549099832922</v>
       </c>
       <c r="D23" s="36">
-        <v>76.866666666666674</v>
+        <v>118.16666666666667</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="29">
-        <v>10801</v>
+        <v>20603</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
       <c r="C24" s="36">
-        <v>13.284446569955897</v>
+        <v>108.15367823525564</v>
       </c>
       <c r="D24" s="36">
-        <v>26.100000000000005</v>
+        <v>73.766666666666666</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="29">
-        <v>10901</v>
+        <v>31205</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>31</v>
+        <v>493</v>
       </c>
       <c r="C25" s="36">
-        <v>143.41619153142292</v>
+        <v>107.16566835573407</v>
       </c>
       <c r="D25" s="36">
-        <v>20.2</v>
+        <v>199.83333333333334</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="29">
-        <v>10902</v>
+        <v>21102</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>32</v>
+        <v>430</v>
       </c>
       <c r="C26" s="36">
-        <v>36.645998581849177</v>
+        <v>103.30612222697971</v>
       </c>
       <c r="D26" s="36">
-        <v>53.933333333333337</v>
+        <v>131.93333333333331</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="29">
-        <v>10903</v>
+        <v>20608</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>33</v>
+        <v>408</v>
       </c>
       <c r="C27" s="36">
-        <v>74.881233248270647</v>
+        <v>102.49370290886453</v>
       </c>
       <c r="D27" s="36">
-        <v>43.666666666666664</v>
+        <v>131.80000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="29">
-        <v>11001</v>
+        <v>21104</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>371</v>
+        <v>432</v>
       </c>
       <c r="C28" s="36">
-        <v>56.684696616888139</v>
+        <v>100.95755906530688</v>
       </c>
       <c r="D28" s="36">
-        <v>14.1</v>
+        <v>179.83333333333334</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="29">
-        <v>11002</v>
+        <v>90101</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>372</v>
+        <v>544</v>
       </c>
       <c r="C29" s="36">
-        <v>0</v>
+        <v>97.011032640562973</v>
       </c>
       <c r="D29" s="36">
-        <v>66.733333333333334</v>
+        <v>91.566666666666677</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="29">
-        <v>11003</v>
+        <v>60301</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>373</v>
+        <v>255</v>
       </c>
       <c r="C30" s="36">
-        <v>11.42026568222971</v>
+        <v>96.2721456873699</v>
       </c>
       <c r="D30" s="36">
-        <v>74.600000000000009</v>
+        <v>120.83333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="29">
-        <v>20101</v>
+        <v>21003</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>374</v>
+        <v>425</v>
       </c>
       <c r="C31" s="36">
-        <v>35.273777214076183</v>
+        <v>95.550463068657749</v>
       </c>
       <c r="D31" s="36">
-        <v>46.933333333333337</v>
+        <v>69.033333333333346</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="29">
-        <v>20102</v>
+        <v>10704</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>375</v>
+        <v>29</v>
       </c>
       <c r="C32" s="36">
-        <v>18.519485543839171</v>
+        <v>94.029606321871725</v>
       </c>
       <c r="D32" s="36">
-        <v>91.266666666666666</v>
+        <v>76.866666666666674</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="29">
-        <v>20103</v>
+        <v>80302</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="C33" s="36">
-        <v>44.464815348917767</v>
+        <v>91.997351102654605</v>
       </c>
       <c r="D33" s="36">
-        <v>32.866666666666667</v>
+        <v>105.63333333333333</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="29">
-        <v>20104</v>
+        <v>70101</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>377</v>
+        <v>264</v>
       </c>
       <c r="C34" s="36">
-        <v>13.873717008348869</v>
+        <v>91.920727200143901</v>
       </c>
       <c r="D34" s="36">
-        <v>93.033333333333346</v>
+        <v>139.76666666666665</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="29">
-        <v>20105</v>
+        <v>20602</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="C35" s="36">
-        <v>40.774580115196365</v>
+        <v>88.942728425699329</v>
       </c>
       <c r="D35" s="36">
-        <v>47.066666666666663</v>
+        <v>172.63333333333333</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="29">
-        <v>20201</v>
+        <v>70302</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>379</v>
+        <v>272</v>
       </c>
       <c r="C36" s="36">
-        <v>75.088581732738405</v>
+        <v>87.937333846640115</v>
       </c>
       <c r="D36" s="36">
-        <v>35.466666666666669</v>
+        <v>71.233333333333334</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="29">
-        <v>20202</v>
+        <v>70104</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>380</v>
+        <v>267</v>
       </c>
       <c r="C37" s="36">
-        <v>23.856326375743411</v>
+        <v>85.724482111952668</v>
       </c>
       <c r="D37" s="36">
-        <v>17.666666666666668</v>
+        <v>148.69999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="29">
-        <v>20203</v>
+        <v>21103</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="C38" s="36">
-        <v>4.43675407072186</v>
+        <v>85.673389417307973</v>
       </c>
       <c r="D38" s="36">
-        <v>0</v>
+        <v>123.83333333333333</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="29">
-        <v>20204</v>
+        <v>70105</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>382</v>
+        <v>268</v>
       </c>
       <c r="C39" s="36">
-        <v>10.056821735530342</v>
+        <v>85.482394630284887</v>
       </c>
       <c r="D39" s="36">
-        <v>0</v>
+        <v>79.366666666666674</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="29">
-        <v>20205</v>
+        <v>20902</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="C40" s="36">
-        <v>55.913350539470969</v>
+        <v>85.408951516977098</v>
       </c>
       <c r="D40" s="36">
-        <v>12.6</v>
+        <v>32.733333333333341</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="29">
-        <v>20206</v>
+        <v>60302</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>384</v>
+        <v>526</v>
       </c>
       <c r="C41" s="36">
-        <v>0</v>
+        <v>82.595915539894563</v>
       </c>
       <c r="D41" s="36">
-        <v>0</v>
+        <v>72.333333333333329</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="29">
-        <v>20301</v>
+        <v>90501</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>385</v>
+        <v>553</v>
       </c>
       <c r="C42" s="36">
-        <v>21.13492945404413</v>
+        <v>80.820709488359839</v>
       </c>
       <c r="D42" s="36">
-        <v>20.3</v>
+        <v>106.90000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="29">
-        <v>20302</v>
+        <v>71106</v>
       </c>
       <c r="B43" s="30" t="s">
-        <v>386</v>
+        <v>310</v>
       </c>
       <c r="C43" s="36">
-        <v>0</v>
+        <v>79.403606249658523</v>
       </c>
       <c r="D43" s="36">
-        <v>9.3000000000000007</v>
+        <v>94.899999999999991</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="29">
-        <v>20303</v>
+        <v>21401</v>
       </c>
       <c r="B44" s="30" t="s">
-        <v>387</v>
+        <v>445</v>
       </c>
       <c r="C44" s="36">
-        <v>71.153811214195031</v>
+        <v>79.024212928989598</v>
       </c>
       <c r="D44" s="36">
-        <v>8.4666666666666668</v>
+        <v>172.96666666666667</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="29">
-        <v>20304</v>
+        <v>80101</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>388</v>
+        <v>320</v>
       </c>
       <c r="C45" s="36">
-        <v>8.5910652920962196</v>
+        <v>77.81096324444259</v>
       </c>
       <c r="D45" s="36">
-        <v>12.299999999999999</v>
+        <v>116.3</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="29">
-        <v>20305</v>
+        <v>60601</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>389</v>
+        <v>494</v>
       </c>
       <c r="C46" s="36">
-        <v>10.918222513374822</v>
+        <v>77.510346644155319</v>
       </c>
       <c r="D46" s="36">
-        <v>14.066666666666668</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="29">
-        <v>20306</v>
+        <v>71104</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>390</v>
+        <v>308</v>
       </c>
       <c r="C47" s="36">
-        <v>0</v>
+        <v>76.776058127348406</v>
       </c>
       <c r="D47" s="36">
-        <v>0</v>
+        <v>97.166666666666671</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="29">
-        <v>20307</v>
+        <v>70102</v>
       </c>
       <c r="B48" s="30" t="s">
-        <v>391</v>
+        <v>265</v>
       </c>
       <c r="C48" s="36">
-        <v>0</v>
+        <v>76.454048372635896</v>
       </c>
       <c r="D48" s="36">
-        <v>0</v>
+        <v>132.33333333333334</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="29">
-        <v>20308</v>
+        <v>70401</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>392</v>
+        <v>274</v>
       </c>
       <c r="C49" s="36">
-        <v>61.581771795548519</v>
+        <v>76.217952445895548</v>
       </c>
       <c r="D49" s="36">
-        <v>8.2666666666666657</v>
+        <v>71.166666666666671</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="29">
-        <v>20401</v>
+        <v>20201</v>
       </c>
       <c r="B50" s="30" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="C50" s="36">
-        <v>11.810252179432171</v>
+        <v>75.088581732738405</v>
       </c>
       <c r="D50" s="36">
-        <v>14.4</v>
+        <v>35.466666666666669</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="29">
-        <v>20402</v>
+        <v>10903</v>
       </c>
       <c r="B51" s="30" t="s">
-        <v>394</v>
+        <v>33</v>
       </c>
       <c r="C51" s="36">
-        <v>12.612966050083253</v>
+        <v>74.881233248270647</v>
       </c>
       <c r="D51" s="36">
-        <v>20.033333333333335</v>
+        <v>43.666666666666664</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="29">
-        <v>20403</v>
+        <v>80304</v>
       </c>
       <c r="B52" s="30" t="s">
-        <v>395</v>
+        <v>541</v>
       </c>
       <c r="C52" s="36">
-        <v>10.246232807689848</v>
+        <v>74.146815154014405</v>
       </c>
       <c r="D52" s="36">
-        <v>13.666666666666666</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="29">
-        <v>20404</v>
+        <v>20303</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C53" s="36">
-        <v>22.967480788226933</v>
+        <v>71.153811214195031</v>
       </c>
       <c r="D53" s="36">
-        <v>9.8666666666666654</v>
+        <v>8.4666666666666668</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="29">
-        <v>20405</v>
+        <v>90303</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>397</v>
+        <v>551</v>
       </c>
       <c r="C54" s="36">
-        <v>6.2583447225920965</v>
+        <v>69.138269149000891</v>
       </c>
       <c r="D54" s="36">
-        <v>9</v>
+        <v>100.26666666666667</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="29">
-        <v>20501</v>
+        <v>70706</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>398</v>
+        <v>289</v>
       </c>
       <c r="C55" s="36">
-        <v>23.177651761447567</v>
+        <v>68.913474092850265</v>
       </c>
       <c r="D55" s="36">
-        <v>16.866666666666667</v>
+        <v>56.133333333333333</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="29">
-        <v>20502</v>
+        <v>71401</v>
       </c>
       <c r="B56" s="30" t="s">
-        <v>399</v>
+        <v>537</v>
       </c>
       <c r="C56" s="36">
-        <v>64.63070641175922</v>
+        <v>68.581038350585018</v>
       </c>
       <c r="D56" s="36">
-        <v>31.566666666666663</v>
+        <v>67.533333333333346</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="29">
-        <v>20503</v>
+        <v>80201</v>
       </c>
       <c r="B57" s="30" t="s">
-        <v>400</v>
+        <v>321</v>
       </c>
       <c r="C57" s="36">
-        <v>53.455260140126022</v>
+        <v>68.313444828510441</v>
       </c>
       <c r="D57" s="36">
-        <v>24.7</v>
+        <v>115.96666666666665</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="29">
-        <v>20601</v>
+        <v>71004</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>401</v>
+        <v>535</v>
       </c>
       <c r="C58" s="36">
-        <v>122.01798038806714</v>
+        <v>68.111893122304522</v>
       </c>
       <c r="D58" s="36">
-        <v>103.86666666666667</v>
+        <v>95.033333333333346</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="29">
-        <v>20602</v>
+        <v>90203</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>402</v>
+        <v>549</v>
       </c>
       <c r="C59" s="36">
-        <v>88.942728425699329</v>
+        <v>67.505794184080472</v>
       </c>
       <c r="D59" s="36">
-        <v>172.63333333333333</v>
+        <v>24.066666666666666</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="29">
-        <v>20603</v>
+        <v>50203</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="C60" s="36">
-        <v>108.15367823525564</v>
+        <v>67.185191953962018</v>
       </c>
       <c r="D60" s="36">
-        <v>73.766666666666666</v>
+        <v>45.599999999999994</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="29">
-        <v>20604</v>
+        <v>21702</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>404</v>
+        <v>452</v>
       </c>
       <c r="C61" s="36">
-        <v>58.011076498232036</v>
+        <v>65.608295966592323</v>
       </c>
       <c r="D61" s="36">
-        <v>94.933333333333337</v>
+        <v>10.933333333333332</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="29">
-        <v>20605</v>
+        <v>20502</v>
       </c>
       <c r="B62" s="30" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C62" s="36">
-        <v>8.934155275618691</v>
+        <v>64.63070641175922</v>
       </c>
       <c r="D62" s="36">
-        <v>62.033333333333331</v>
+        <v>31.566666666666663</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="29">
-        <v>20606</v>
+        <v>80202</v>
       </c>
       <c r="B63" s="30" t="s">
-        <v>406</v>
+        <v>540</v>
       </c>
       <c r="C63" s="36">
-        <v>340.05362762099861</v>
+        <v>64.459058153270021</v>
       </c>
       <c r="D63" s="36">
-        <v>433.36666666666662</v>
+        <v>114.56666666666666</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="29">
-        <v>20607</v>
+        <v>10703</v>
       </c>
       <c r="B64" s="30" t="s">
-        <v>407</v>
+        <v>28</v>
       </c>
       <c r="C64" s="36">
-        <v>117.62798904714681</v>
+        <v>63.846394167045865</v>
       </c>
       <c r="D64" s="36">
-        <v>218.83333333333334</v>
+        <v>63.466666666666661</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="29">
-        <v>20608</v>
+        <v>40701</v>
       </c>
       <c r="B65" s="30" t="s">
-        <v>408</v>
+        <v>191</v>
       </c>
       <c r="C65" s="36">
-        <v>102.49370290886453</v>
+        <v>62.887958163078423</v>
       </c>
       <c r="D65" s="36">
-        <v>131.80000000000001</v>
+        <v>54.666666666666664</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="29">
-        <v>20701</v>
+        <v>71005</v>
       </c>
       <c r="B66" s="30" t="s">
-        <v>409</v>
+        <v>304</v>
       </c>
       <c r="C66" s="36">
-        <v>55.532826204435828</v>
+        <v>62.469063006639708</v>
       </c>
       <c r="D66" s="36">
-        <v>36.466666666666669</v>
+        <v>88.066666666666677</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="29">
-        <v>20702</v>
+        <v>90201</v>
       </c>
       <c r="B67" s="30" t="s">
-        <v>410</v>
+        <v>548</v>
       </c>
       <c r="C67" s="36">
-        <v>34.789699033316971</v>
+        <v>62.334971357668138</v>
       </c>
       <c r="D67" s="36">
-        <v>8.9666666666666668</v>
+        <v>33.93333333333333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="29">
-        <v>20801</v>
+        <v>30701</v>
       </c>
       <c r="B68" s="30" t="s">
-        <v>411</v>
+        <v>475</v>
       </c>
       <c r="C68" s="36">
-        <v>14.575271881732673</v>
+        <v>61.730389482302662</v>
       </c>
       <c r="D68" s="36">
-        <v>56.866666666666667</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="29">
-        <v>20802</v>
+        <v>20308</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="C69" s="36">
-        <v>20.521079953911396</v>
+        <v>61.581771795548519</v>
       </c>
       <c r="D69" s="36">
-        <v>12.9</v>
+        <v>8.2666666666666657</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="29">
-        <v>20803</v>
+        <v>71501</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>413</v>
+        <v>539</v>
       </c>
       <c r="C70" s="36">
-        <v>12.331888292981178</v>
+        <v>61.028728452556805</v>
       </c>
       <c r="D70" s="36">
-        <v>30.733333333333334</v>
+        <v>80.600000000000009</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="29">
-        <v>20804</v>
+        <v>10302</v>
       </c>
       <c r="B71" s="30" t="s">
-        <v>414</v>
+        <v>14</v>
       </c>
       <c r="C71" s="36">
-        <v>4.3504742016879847</v>
+        <v>59.678832075248657</v>
       </c>
       <c r="D71" s="36">
-        <v>22.333333333333332</v>
+        <v>63.166666666666664</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="29">
-        <v>20805</v>
+        <v>71003</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>415</v>
+        <v>302</v>
       </c>
       <c r="C72" s="36">
-        <v>3.8202204267186217</v>
+        <v>58.663047991285538</v>
       </c>
       <c r="D72" s="36">
-        <v>11.133333333333333</v>
+        <v>95.566666666666677</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="29">
-        <v>20806</v>
+        <v>90302</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>416</v>
+        <v>260</v>
       </c>
       <c r="C73" s="36">
-        <v>35.983309259912964</v>
+        <v>58.578743315801695</v>
       </c>
       <c r="D73" s="36">
-        <v>13.966666666666667</v>
+        <v>17.566666666666666</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="29">
-        <v>20807</v>
+        <v>20604</v>
       </c>
       <c r="B74" s="30" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="C74" s="36">
-        <v>29.10502033458576</v>
+        <v>58.011076498232036</v>
       </c>
       <c r="D74" s="36">
-        <v>15.366666666666667</v>
+        <v>94.933333333333337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="29">
-        <v>20901</v>
+        <v>21502</v>
       </c>
       <c r="B75" s="30" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="C75" s="36">
-        <v>20.046047740199544</v>
+        <v>57.793747260902116</v>
       </c>
       <c r="D75" s="36">
-        <v>65.366666666666674</v>
+        <v>96.066666666666663</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="29">
-        <v>20902</v>
+        <v>70903</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>419</v>
+        <v>298</v>
       </c>
       <c r="C76" s="36">
-        <v>85.408951516977098</v>
+        <v>57.574855237580927</v>
       </c>
       <c r="D76" s="36">
-        <v>32.733333333333341</v>
+        <v>33.06666666666667</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="29">
-        <v>20903</v>
+        <v>11001</v>
       </c>
       <c r="B77" s="30" t="s">
-        <v>420</v>
+        <v>371</v>
       </c>
       <c r="C77" s="36">
-        <v>14.059356083895016</v>
+        <v>56.684696616888139</v>
       </c>
       <c r="D77" s="36">
-        <v>8.6666666666666661</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="29">
-        <v>20904</v>
+        <v>20205</v>
       </c>
       <c r="B78" s="30" t="s">
-        <v>421</v>
+        <v>383</v>
       </c>
       <c r="C78" s="36">
-        <v>14.872305567630548</v>
+        <v>55.913350539470969</v>
       </c>
       <c r="D78" s="36">
-        <v>10.833333333333334</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="29">
-        <v>20905</v>
+        <v>20701</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="C79" s="36">
-        <v>42.405306466035491</v>
+        <v>55.532826204435828</v>
       </c>
       <c r="D79" s="36">
-        <v>20.766666666666666</v>
+        <v>36.466666666666669</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="29">
-        <v>21001</v>
+        <v>10403</v>
       </c>
       <c r="B80" s="30" t="s">
-        <v>423</v>
+        <v>19</v>
       </c>
       <c r="C80" s="36">
-        <v>39.13448704743103</v>
+        <v>55.45445770337367</v>
       </c>
       <c r="D80" s="36">
-        <v>29.599999999999998</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="29">
-        <v>21002</v>
+        <v>70402</v>
       </c>
       <c r="B81" s="30" t="s">
-        <v>424</v>
+        <v>275</v>
       </c>
       <c r="C81" s="36">
-        <v>19.975164068130518</v>
+        <v>54.900778777965236</v>
       </c>
       <c r="D81" s="36">
-        <v>35.199999999999996</v>
+        <v>68.899999999999991</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="29">
-        <v>21003</v>
+        <v>71002</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>425</v>
+        <v>534</v>
       </c>
       <c r="C82" s="36">
-        <v>95.550463068657749</v>
+        <v>54.693719583428468</v>
       </c>
       <c r="D82" s="36">
-        <v>69.033333333333346</v>
+        <v>58.733333333333327</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="29">
-        <v>21004</v>
+        <v>70503</v>
       </c>
       <c r="B83" s="30" t="s">
-        <v>426</v>
+        <v>280</v>
       </c>
       <c r="C83" s="36">
-        <v>11.28924042075637</v>
+        <v>54.664561462933271</v>
       </c>
       <c r="D83" s="36">
-        <v>1.9333333333333333</v>
+        <v>36.233333333333327</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="29">
-        <v>21005</v>
+        <v>70404</v>
       </c>
       <c r="B84" s="30" t="s">
-        <v>427</v>
+        <v>529</v>
       </c>
       <c r="C84" s="36">
-        <v>4.2625745950554128</v>
+        <v>54.151105716268866</v>
       </c>
       <c r="D84" s="36">
-        <v>9.7999999999999989</v>
+        <v>45.966666666666669</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="29">
-        <v>21006</v>
+        <v>90301</v>
       </c>
       <c r="B85" s="30" t="s">
-        <v>428</v>
+        <v>550</v>
       </c>
       <c r="C85" s="36">
-        <v>33.052911170291708</v>
+        <v>53.59056806002144</v>
       </c>
       <c r="D85" s="36">
-        <v>41.9</v>
+        <v>27.366666666666664</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="29">
-        <v>21101</v>
+        <v>20503</v>
       </c>
       <c r="B86" s="30" t="s">
-        <v>429</v>
+        <v>400</v>
       </c>
       <c r="C86" s="36">
-        <v>114.13715864761683</v>
+        <v>53.455260140126022</v>
       </c>
       <c r="D86" s="36">
-        <v>194.26666666666665</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="29">
-        <v>21102</v>
+        <v>51103</v>
       </c>
       <c r="B87" s="30" t="s">
-        <v>430</v>
+        <v>239</v>
       </c>
       <c r="C87" s="36">
-        <v>103.30612222697971</v>
+        <v>52.721380838268381</v>
       </c>
       <c r="D87" s="36">
-        <v>131.93333333333331</v>
+        <v>18.633333333333336</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="29">
-        <v>21103</v>
+        <v>80102</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>431</v>
+        <v>306</v>
       </c>
       <c r="C88" s="36">
-        <v>85.673389417307973</v>
+        <v>51.382930652510332</v>
       </c>
       <c r="D88" s="36">
-        <v>123.83333333333333</v>
+        <v>32.966666666666669</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="29">
-        <v>21104</v>
+        <v>71201</v>
       </c>
       <c r="B89" s="30" t="s">
-        <v>432</v>
+        <v>536</v>
       </c>
       <c r="C89" s="36">
-        <v>100.95755906530688</v>
+        <v>51.305787731609655</v>
       </c>
       <c r="D89" s="36">
-        <v>179.83333333333334</v>
+        <v>33.266666666666673</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="29">
-        <v>21105</v>
+        <v>10201</v>
       </c>
       <c r="B90" s="30" t="s">
-        <v>433</v>
+        <v>365</v>
       </c>
       <c r="C90" s="36">
-        <v>125.18333198810002</v>
+        <v>51.206758404444997</v>
       </c>
       <c r="D90" s="36">
-        <v>185.33333333333334</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="29">
-        <v>21201</v>
+        <v>10701</v>
       </c>
       <c r="B91" s="30" t="s">
-        <v>434</v>
+        <v>26</v>
       </c>
       <c r="C91" s="36">
-        <v>22.87855304905834</v>
+        <v>50.573331570098809</v>
       </c>
       <c r="D91" s="36">
-        <v>32.266666666666666</v>
+        <v>34.333333333333336</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="29">
-        <v>21202</v>
+        <v>10601</v>
       </c>
       <c r="B92" s="30" t="s">
-        <v>435</v>
+        <v>24</v>
       </c>
       <c r="C92" s="36">
-        <v>6.9701185033158</v>
+        <v>49.552111627744544</v>
       </c>
       <c r="D92" s="36">
-        <v>20.833333333333332</v>
+        <v>47.866666666666667</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="29">
-        <v>21203</v>
+        <v>10103</v>
       </c>
       <c r="B93" s="30" t="s">
-        <v>436</v>
+        <v>364</v>
       </c>
       <c r="C93" s="36">
-        <v>19.358460356025745</v>
+        <v>48.775773236622378</v>
       </c>
       <c r="D93" s="36">
-        <v>29.2</v>
+        <v>35.93333333333333</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="29">
-        <v>21204</v>
+        <v>70902</v>
       </c>
       <c r="B94" s="30" t="s">
-        <v>437</v>
+        <v>297</v>
       </c>
       <c r="C94" s="36">
-        <v>0</v>
+        <v>48.729633244673494</v>
       </c>
       <c r="D94" s="36">
-        <v>17.400000000000002</v>
+        <v>53.800000000000004</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="29">
-        <v>21301</v>
+        <v>31403</v>
       </c>
       <c r="B95" s="30" t="s">
-        <v>438</v>
+        <v>501</v>
       </c>
       <c r="C95" s="36">
-        <v>16.578410405949786</v>
+        <v>48.417078270236722</v>
       </c>
       <c r="D95" s="36">
-        <v>19.566666666666666</v>
+        <v>40.533333333333331</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="29">
-        <v>21302</v>
+        <v>50901</v>
       </c>
       <c r="B96" s="30" t="s">
-        <v>439</v>
+        <v>232</v>
       </c>
       <c r="C96" s="36">
-        <v>9.2361688371663444</v>
+        <v>48.197227734106747</v>
       </c>
       <c r="D96" s="36">
-        <v>11.633333333333333</v>
+        <v>7.4666666666666659</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="29">
-        <v>21303</v>
+        <v>70702</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>440</v>
+        <v>285</v>
       </c>
       <c r="C97" s="36">
-        <v>4.274600324869624</v>
+        <v>48.049724561338543</v>
       </c>
       <c r="D97" s="36">
-        <v>19.900000000000002</v>
+        <v>28.933333333333337</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="29">
-        <v>21304</v>
+        <v>50601</v>
       </c>
       <c r="B98" s="30" t="s">
-        <v>441</v>
+        <v>226</v>
       </c>
       <c r="C98" s="36">
-        <v>34.143106595308645</v>
+        <v>47.363232260126516</v>
       </c>
       <c r="D98" s="36">
-        <v>9.2666666666666675</v>
+        <v>65.933333333333337</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="29">
-        <v>21305</v>
+        <v>50602</v>
       </c>
       <c r="B99" s="30" t="s">
-        <v>442</v>
+        <v>522</v>
       </c>
       <c r="C99" s="36">
-        <v>13.900323818807957</v>
+        <v>46.572575636112255</v>
       </c>
       <c r="D99" s="36">
-        <v>32.866666666666667</v>
+        <v>25.566666666666663</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="29">
-        <v>21306</v>
+        <v>51301</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>443</v>
+        <v>243</v>
       </c>
       <c r="C100" s="36">
-        <v>6.8131493783001185</v>
+        <v>46.554981456369291</v>
       </c>
       <c r="D100" s="36">
-        <v>20.533333333333331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="29">
-        <v>21307</v>
+        <v>10702</v>
       </c>
       <c r="B101" s="30" t="s">
-        <v>444</v>
+        <v>27</v>
       </c>
       <c r="C101" s="36">
-        <v>14.703712253182355</v>
+        <v>46.449535089086275</v>
       </c>
       <c r="D101" s="36">
-        <v>34.4</v>
+        <v>56.233333333333327</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="29">
-        <v>21401</v>
+        <v>50201</v>
       </c>
       <c r="B102" s="30" t="s">
-        <v>445</v>
+        <v>518</v>
       </c>
       <c r="C102" s="36">
-        <v>79.024212928989598</v>
+        <v>45.938166229086335</v>
       </c>
       <c r="D102" s="36">
-        <v>172.96666666666667</v>
+        <v>12.866666666666667</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="29">
-        <v>21402</v>
+        <v>70602</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>446</v>
+        <v>282</v>
       </c>
       <c r="C103" s="36">
-        <v>117.16708649386037</v>
+        <v>45.839798964581007</v>
       </c>
       <c r="D103" s="36">
-        <v>161.30000000000001</v>
+        <v>60.833333333333336</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="29">
-        <v>21501</v>
+        <v>10301</v>
       </c>
       <c r="B104" s="30" t="s">
-        <v>447</v>
+        <v>366</v>
       </c>
       <c r="C104" s="36">
-        <v>35.780976698426947</v>
+        <v>45.763307149606995</v>
       </c>
       <c r="D104" s="36">
-        <v>58.4</v>
+        <v>61.199999999999996</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="29">
-        <v>21502</v>
+        <v>50802</v>
       </c>
       <c r="B105" s="30" t="s">
-        <v>448</v>
+        <v>231</v>
       </c>
       <c r="C105" s="36">
-        <v>57.793747260902116</v>
+        <v>45.396801580733957</v>
       </c>
       <c r="D105" s="36">
-        <v>96.066666666666663</v>
+        <v>36.200000000000003</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="29">
-        <v>21601</v>
+        <v>50204</v>
       </c>
       <c r="B106" s="30" t="s">
-        <v>449</v>
+        <v>519</v>
       </c>
       <c r="C106" s="36">
-        <v>38.018841243229964</v>
+        <v>44.931449145075014</v>
       </c>
       <c r="D106" s="36">
-        <v>46.9</v>
+        <v>88.466666666666654</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="29">
-        <v>21602</v>
+        <v>20103</v>
       </c>
       <c r="B107" s="30" t="s">
-        <v>450</v>
+        <v>376</v>
       </c>
       <c r="C107" s="36">
-        <v>22.14833355481667</v>
+        <v>44.464815348917767</v>
       </c>
       <c r="D107" s="36">
-        <v>0</v>
+        <v>32.866666666666667</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="29">
-        <v>21701</v>
+        <v>30702</v>
       </c>
       <c r="B108" s="30" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C108" s="36">
-        <v>8.7599664792326504</v>
+        <v>44.385402138617032</v>
       </c>
       <c r="D108" s="36">
-        <v>39.800000000000004</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="29">
-        <v>21702</v>
+        <v>20905</v>
       </c>
       <c r="B109" s="30" t="s">
-        <v>452</v>
+        <v>422</v>
       </c>
       <c r="C109" s="36">
-        <v>65.608295966592323</v>
+        <v>42.405306466035491</v>
       </c>
       <c r="D109" s="36">
-        <v>10.933333333333332</v>
+        <v>20.766666666666666</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="29">
-        <v>21703</v>
+        <v>31401</v>
       </c>
       <c r="B110" s="30" t="s">
-        <v>453</v>
+        <v>499</v>
       </c>
       <c r="C110" s="36">
-        <v>4.5749839875560427</v>
+        <v>41.907897573192095</v>
       </c>
       <c r="D110" s="36">
-        <v>36.300000000000004</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="29">
-        <v>21801</v>
+        <v>71103</v>
       </c>
       <c r="B111" s="30" t="s">
-        <v>454</v>
+        <v>307</v>
       </c>
       <c r="C111" s="36">
-        <v>235.00507397318805</v>
+        <v>41.840631450434287</v>
       </c>
       <c r="D111" s="36">
-        <v>4.6000000000000005</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="29">
-        <v>21802</v>
+        <v>90401</v>
       </c>
       <c r="B112" s="30" t="s">
-        <v>455</v>
+        <v>325</v>
       </c>
       <c r="C112" s="36">
-        <v>4.2977479800584497</v>
+        <v>41.753653444676409</v>
       </c>
       <c r="D112" s="36">
-        <v>0</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="29">
-        <v>21803</v>
+        <v>70603</v>
       </c>
       <c r="B113" s="30" t="s">
-        <v>456</v>
+        <v>283</v>
       </c>
       <c r="C113" s="36">
-        <v>0</v>
+        <v>41.61935625593636</v>
       </c>
       <c r="D113" s="36">
-        <v>0</v>
+        <v>33.366666666666667</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="29">
-        <v>21901</v>
+        <v>70703</v>
       </c>
       <c r="B114" s="30" t="s">
-        <v>457</v>
+        <v>286</v>
       </c>
       <c r="C114" s="36">
-        <v>10.19936763920637</v>
+        <v>41.498203907418542</v>
       </c>
       <c r="D114" s="36">
-        <v>0</v>
+        <v>45.699999999999996</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="29">
-        <v>21902</v>
+        <v>20105</v>
       </c>
       <c r="B115" s="30" t="s">
-        <v>458</v>
+        <v>378</v>
       </c>
       <c r="C115" s="36">
-        <v>0</v>
+        <v>40.774580115196365</v>
       </c>
       <c r="D115" s="36">
-        <v>19.633333333333333</v>
+        <v>47.066666666666663</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="29">
-        <v>22001</v>
+        <v>30901</v>
       </c>
       <c r="B116" s="30" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="C116" s="36">
-        <v>127.76093843136567</v>
+        <v>40.772448534780203</v>
       </c>
       <c r="D116" s="36">
-        <v>316.83333333333331</v>
+        <v>50.70000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="29">
-        <v>22002</v>
+        <v>10101</v>
       </c>
       <c r="B117" s="30" t="s">
-        <v>460</v>
+        <v>8</v>
       </c>
       <c r="C117" s="36">
-        <v>138.32329700374385</v>
+        <v>40.324561058351229</v>
       </c>
       <c r="D117" s="36">
-        <v>132.5</v>
+        <v>40.533333333333331</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="29">
-        <v>30101</v>
+        <v>70501</v>
       </c>
       <c r="B118" s="30" t="s">
-        <v>358</v>
+        <v>530</v>
       </c>
       <c r="C118" s="36">
-        <v>35.120990720257261</v>
+        <v>39.920293720951378</v>
       </c>
       <c r="D118" s="36">
-        <v>44.93333333333333</v>
+        <v>43.933333333333337</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="29">
-        <v>30201</v>
+        <v>10501</v>
       </c>
       <c r="B119" s="30" t="s">
-        <v>461</v>
+        <v>22</v>
       </c>
       <c r="C119" s="36">
-        <v>18.349234179078731</v>
+        <v>39.499227389632154</v>
       </c>
       <c r="D119" s="36">
-        <v>28.366666666666664</v>
+        <v>37.033333333333331</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="29">
-        <v>30202</v>
+        <v>90503</v>
       </c>
       <c r="B120" s="30" t="s">
-        <v>462</v>
+        <v>555</v>
       </c>
       <c r="C120" s="36">
-        <v>0</v>
+        <v>39.424403705893951</v>
       </c>
       <c r="D120" s="36">
-        <v>0</v>
+        <v>12.366666666666667</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="29">
-        <v>30203</v>
+        <v>60101</v>
       </c>
       <c r="B121" s="30" t="s">
-        <v>463</v>
+        <v>359</v>
       </c>
       <c r="C121" s="36">
-        <v>23.813315929731875</v>
+        <v>39.306624979784942</v>
       </c>
       <c r="D121" s="36">
-        <v>73.7</v>
+        <v>49.166666666666664</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="29">
-        <v>30301</v>
+        <v>50101</v>
       </c>
       <c r="B122" s="30" t="s">
-        <v>464</v>
+        <v>209</v>
       </c>
       <c r="C122" s="36">
-        <v>24.522721483327231</v>
+        <v>39.288922384088487</v>
       </c>
       <c r="D122" s="36">
-        <v>35.666666666666664</v>
+        <v>50.433333333333337</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="29">
-        <v>30302</v>
+        <v>21001</v>
       </c>
       <c r="B123" s="30" t="s">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="C123" s="36">
-        <v>8.2827528193260829</v>
+        <v>39.13448704743103</v>
       </c>
       <c r="D123" s="36">
-        <v>9.5333333333333332</v>
+        <v>29.599999999999998</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="29">
-        <v>30303</v>
+        <v>31001</v>
       </c>
       <c r="B124" s="30" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="C124" s="36">
-        <v>9.1411024576170004</v>
+        <v>38.923617032286792</v>
       </c>
       <c r="D124" s="36">
-        <v>3.8000000000000003</v>
+        <v>59.166666666666664</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="29">
-        <v>30401</v>
+        <v>70202</v>
       </c>
       <c r="B125" s="30" t="s">
-        <v>467</v>
+        <v>270</v>
       </c>
       <c r="C125" s="36">
-        <v>29.924630621863855</v>
+        <v>38.050481019962739</v>
       </c>
       <c r="D125" s="36">
-        <v>36.466666666666669</v>
+        <v>61.699999999999996</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="29">
-        <v>30402</v>
+        <v>21601</v>
       </c>
       <c r="B126" s="30" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="C126" s="36">
-        <v>22.331737100336895</v>
+        <v>38.018841243229964</v>
       </c>
       <c r="D126" s="36">
-        <v>32.333333333333336</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="29">
-        <v>30403</v>
+        <v>71403</v>
       </c>
       <c r="B127" s="30" t="s">
-        <v>469</v>
+        <v>538</v>
       </c>
       <c r="C127" s="36">
-        <v>34.415382619918859</v>
+        <v>37.839357064572937</v>
       </c>
       <c r="D127" s="36">
-        <v>42.733333333333327</v>
+        <v>33</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="29">
-        <v>30404</v>
+        <v>30904</v>
       </c>
       <c r="B128" s="30" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="C128" s="36">
-        <v>0</v>
+        <v>37.685788805597277</v>
       </c>
       <c r="D128" s="36">
-        <v>31.7</v>
+        <v>64.466666666666654</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="29">
-        <v>30501</v>
+        <v>80701</v>
       </c>
       <c r="B129" s="30" t="s">
-        <v>471</v>
+        <v>332</v>
       </c>
       <c r="C129" s="36">
-        <v>3.333666700003334</v>
+        <v>37.456664355715738</v>
       </c>
       <c r="D129" s="36">
-        <v>32.233333333333327</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="29">
-        <v>30502</v>
+        <v>80401</v>
       </c>
       <c r="B130" s="30" t="s">
-        <v>472</v>
+        <v>327</v>
       </c>
       <c r="C130" s="36">
-        <v>10.480853099237502</v>
+        <v>37.310163037142893</v>
       </c>
       <c r="D130" s="36">
-        <v>37.033333333333331</v>
+        <v>23.400000000000002</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="29">
-        <v>30601</v>
+        <v>10902</v>
       </c>
       <c r="B131" s="30" t="s">
-        <v>473</v>
+        <v>32</v>
       </c>
       <c r="C131" s="36">
-        <v>14.319320579371373</v>
+        <v>36.645998581849177</v>
       </c>
       <c r="D131" s="36">
-        <v>16.733333333333334</v>
+        <v>53.933333333333337</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="29">
-        <v>30602</v>
+        <v>20806</v>
       </c>
       <c r="B132" s="30" t="s">
-        <v>474</v>
+        <v>416</v>
       </c>
       <c r="C132" s="36">
-        <v>8.6471251595714005</v>
+        <v>35.983309259912964</v>
       </c>
       <c r="D132" s="36">
-        <v>8.9</v>
+        <v>13.966666666666667</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="29">
-        <v>30701</v>
+        <v>21501</v>
       </c>
       <c r="B133" s="30" t="s">
-        <v>475</v>
+        <v>447</v>
       </c>
       <c r="C133" s="36">
-        <v>61.730389482302662</v>
+        <v>35.780976698426947</v>
       </c>
       <c r="D133" s="36">
-        <v>61.1</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="29">
-        <v>30702</v>
+        <v>20101</v>
       </c>
       <c r="B134" s="30" t="s">
-        <v>476</v>
+        <v>374</v>
       </c>
       <c r="C134" s="36">
-        <v>44.385402138617032</v>
+        <v>35.273777214076183</v>
       </c>
       <c r="D134" s="36">
-        <v>24.8</v>
+        <v>46.933333333333337</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="29">
-        <v>30703</v>
+        <v>30101</v>
       </c>
       <c r="B135" s="30" t="s">
-        <v>477</v>
+        <v>358</v>
       </c>
       <c r="C135" s="36">
-        <v>25.031289111389238</v>
+        <v>35.120990720257261</v>
       </c>
       <c r="D135" s="36">
-        <v>34.233333333333327</v>
+        <v>44.93333333333333</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="29">
-        <v>30801</v>
+        <v>20702</v>
       </c>
       <c r="B136" s="30" t="s">
-        <v>478</v>
+        <v>410</v>
       </c>
       <c r="C136" s="36">
-        <v>33.046428475683321</v>
+        <v>34.789699033316971</v>
       </c>
       <c r="D136" s="36">
-        <v>37.166666666666671</v>
+        <v>8.9666666666666668</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="29">
-        <v>30802</v>
+        <v>71102</v>
       </c>
       <c r="B137" s="30" t="s">
-        <v>479</v>
+        <v>306</v>
       </c>
       <c r="C137" s="36">
-        <v>24.393708206615816</v>
+        <v>34.737295069339176</v>
       </c>
       <c r="D137" s="36">
-        <v>29.600000000000005</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="29">
-        <v>30803</v>
+        <v>30403</v>
       </c>
       <c r="B138" s="30" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="C138" s="36">
-        <v>26.756346646297885</v>
+        <v>34.415382619918859</v>
       </c>
       <c r="D138" s="36">
-        <v>16.433333333333334</v>
+        <v>42.733333333333327</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="29">
-        <v>30901</v>
+        <v>80702</v>
       </c>
       <c r="B139" s="30" t="s">
-        <v>481</v>
+        <v>307</v>
       </c>
       <c r="C139" s="36">
-        <v>40.772448534780203</v>
+        <v>34.16648480285405</v>
       </c>
       <c r="D139" s="36">
-        <v>50.70000000000001</v>
+        <v>50.066666666666663</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="29">
-        <v>30902</v>
+        <v>21304</v>
       </c>
       <c r="B140" s="30" t="s">
-        <v>482</v>
+        <v>441</v>
       </c>
       <c r="C140" s="36">
-        <v>33.315003784405953</v>
+        <v>34.143106595308645</v>
       </c>
       <c r="D140" s="36">
-        <v>70.766666666666666</v>
+        <v>9.2666666666666675</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="29">
-        <v>30903</v>
+        <v>80602</v>
       </c>
       <c r="B141" s="30" t="s">
-        <v>483</v>
+        <v>331</v>
       </c>
       <c r="C141" s="36">
-        <v>23.808336547770903</v>
+        <v>33.555737886852107</v>
       </c>
       <c r="D141" s="36">
-        <v>42</v>
+        <v>36.966666666666669</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="29">
-        <v>30904</v>
+        <v>60201</v>
       </c>
       <c r="B142" s="30" t="s">
-        <v>484</v>
+        <v>253</v>
       </c>
       <c r="C142" s="36">
-        <v>37.685788805597277</v>
+        <v>33.476683093558798</v>
       </c>
       <c r="D142" s="36">
-        <v>64.466666666666654</v>
+        <v>20.866666666666664</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="29">
-        <v>30905</v>
+        <v>30902</v>
       </c>
       <c r="B143" s="30" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C143" s="36">
-        <v>23.396648984812416</v>
+        <v>33.315003784405953</v>
       </c>
       <c r="D143" s="36">
-        <v>67.3</v>
+        <v>70.766666666666666</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="29">
-        <v>31001</v>
+        <v>21006</v>
       </c>
       <c r="B144" s="30" t="s">
-        <v>486</v>
+        <v>428</v>
       </c>
       <c r="C144" s="36">
-        <v>38.923617032286792</v>
+        <v>33.052911170291708</v>
       </c>
       <c r="D144" s="36">
-        <v>59.166666666666664</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="29">
-        <v>31002</v>
+        <v>30801</v>
       </c>
       <c r="B145" s="30" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="C145" s="36">
-        <v>15.485122623131119</v>
+        <v>33.046428475683321</v>
       </c>
       <c r="D145" s="36">
-        <v>29.833333333333332</v>
+        <v>37.166666666666671</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="29">
-        <v>31003</v>
+        <v>60501</v>
       </c>
       <c r="B146" s="30" t="s">
-        <v>488</v>
+        <v>260</v>
       </c>
       <c r="C146" s="36">
-        <v>144.65881280349035</v>
+        <v>32.678816542882352</v>
       </c>
       <c r="D146" s="36">
-        <v>121.13333333333333</v>
+        <v>46.033333333333339</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="29">
-        <v>31101</v>
+        <v>80501</v>
       </c>
       <c r="B147" s="30" t="s">
-        <v>489</v>
+        <v>329</v>
       </c>
       <c r="C147" s="36">
-        <v>18.242665665561393</v>
+        <v>31.568567566214494</v>
       </c>
       <c r="D147" s="36">
-        <v>20.566666666666666</v>
+        <v>59.166666666666664</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="29">
-        <v>31201</v>
+        <v>50404</v>
       </c>
       <c r="B148" s="30" t="s">
-        <v>202</v>
+        <v>521</v>
       </c>
       <c r="C148" s="36">
-        <v>18.721746579771555</v>
+        <v>30.718658903726382</v>
       </c>
       <c r="D148" s="36">
-        <v>20.866666666666667</v>
+        <v>32.699999999999996</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="29">
-        <v>31202</v>
+        <v>31301</v>
       </c>
       <c r="B149" s="30" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C149" s="36">
-        <v>147.50306807283704</v>
+        <v>30.462180664334074</v>
       </c>
       <c r="D149" s="36">
-        <v>26.333333333333332</v>
+        <v>50.433333333333337</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="29">
-        <v>31203</v>
+        <v>70103</v>
       </c>
       <c r="B150" s="30" t="s">
-        <v>491</v>
+        <v>266</v>
       </c>
       <c r="C150" s="36">
-        <v>8.7391062138250746</v>
+        <v>30.35983188671122</v>
       </c>
       <c r="D150" s="36">
-        <v>21.466666666666669</v>
+        <v>68.86666666666666</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="29">
-        <v>31204</v>
+        <v>70301</v>
       </c>
       <c r="B151" s="30" t="s">
-        <v>492</v>
+        <v>271</v>
       </c>
       <c r="C151" s="36">
-        <v>114.6362595260177</v>
+        <v>30.335433771763405</v>
       </c>
       <c r="D151" s="36">
-        <v>206.73333333333335</v>
+        <v>40.133333333333333</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="29">
-        <v>31205</v>
+        <v>30401</v>
       </c>
       <c r="B152" s="30" t="s">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="C152" s="36">
-        <v>107.16566835573407</v>
+        <v>29.924630621863855</v>
       </c>
       <c r="D152" s="36">
-        <v>199.83333333333334</v>
+        <v>36.466666666666669</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="29">
-        <v>31206</v>
+        <v>10102</v>
       </c>
       <c r="B153" s="30" t="s">
-        <v>494</v>
+        <v>9</v>
       </c>
       <c r="C153" s="36">
-        <v>138.27360567027779</v>
+        <v>29.783315852938625</v>
       </c>
       <c r="D153" s="36">
-        <v>199.20000000000002</v>
+        <v>44</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="29">
-        <v>31301</v>
+        <v>70707</v>
       </c>
       <c r="B154" s="30" t="s">
-        <v>495</v>
+        <v>290</v>
       </c>
       <c r="C154" s="36">
-        <v>30.462180664334074</v>
+        <v>29.72762157843253</v>
       </c>
       <c r="D154" s="36">
-        <v>50.433333333333337</v>
+        <v>87.433333333333337</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="29">
-        <v>31302</v>
+        <v>50902</v>
       </c>
       <c r="B155" s="30" t="s">
-        <v>496</v>
+        <v>233</v>
       </c>
       <c r="C155" s="36">
-        <v>6.106124442816145</v>
+        <v>29.63178005033264</v>
       </c>
       <c r="D155" s="36">
-        <v>52.333333333333336</v>
+        <v>44.933333333333337</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="29">
-        <v>31303</v>
+        <v>20807</v>
       </c>
       <c r="B156" s="30" t="s">
-        <v>497</v>
+        <v>417</v>
       </c>
       <c r="C156" s="36">
-        <v>0</v>
+        <v>29.10502033458576</v>
       </c>
       <c r="D156" s="36">
-        <v>0</v>
+        <v>15.366666666666667</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="29">
-        <v>31304</v>
+        <v>70901</v>
       </c>
       <c r="B157" s="30" t="s">
-        <v>498</v>
+        <v>296</v>
       </c>
       <c r="C157" s="36">
-        <v>0</v>
+        <v>28.894956186204894</v>
       </c>
       <c r="D157" s="36">
-        <v>0</v>
+        <v>43.733333333333327</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="29">
-        <v>31401</v>
+        <v>51402</v>
       </c>
       <c r="B158" s="30" t="s">
-        <v>499</v>
+        <v>246</v>
       </c>
       <c r="C158" s="36">
-        <v>41.907897573192095</v>
+        <v>28.851975044571049</v>
       </c>
       <c r="D158" s="36">
-        <v>29.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="29">
-        <v>31402</v>
+        <v>70601</v>
       </c>
       <c r="B159" s="30" t="s">
-        <v>500</v>
+        <v>281</v>
       </c>
       <c r="C159" s="36">
-        <v>10.111111714811059</v>
+        <v>28.743371214963862</v>
       </c>
       <c r="D159" s="36">
-        <v>74.899999999999991</v>
+        <v>30</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="29">
-        <v>31403</v>
+        <v>71101</v>
       </c>
       <c r="B160" s="30" t="s">
-        <v>501</v>
+        <v>305</v>
       </c>
       <c r="C160" s="36">
-        <v>48.417078270236722</v>
+        <v>28.120551419240041</v>
       </c>
       <c r="D160" s="36">
-        <v>40.533333333333331</v>
+        <v>42.466666666666669</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="29">
-        <v>31404</v>
+        <v>50103</v>
       </c>
       <c r="B161" s="30" t="s">
-        <v>502</v>
+        <v>211</v>
       </c>
       <c r="C161" s="36">
-        <v>0</v>
+        <v>28.103945274208328</v>
       </c>
       <c r="D161" s="36">
-        <v>0</v>
+        <v>30.233333333333331</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="29">
-        <v>31405</v>
+        <v>51102</v>
       </c>
       <c r="B162" s="30" t="s">
-        <v>503</v>
+        <v>238</v>
       </c>
       <c r="C162" s="36">
-        <v>17.940437746681017</v>
+        <v>27.830858921333164</v>
       </c>
       <c r="D162" s="36">
-        <v>0</v>
+        <v>63.066666666666663</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="29">
-        <v>31501</v>
+        <v>40101</v>
       </c>
       <c r="B163" s="30" t="s">
-        <v>504</v>
+        <v>173</v>
       </c>
       <c r="C163" s="36">
-        <v>9.5848476751636227</v>
+        <v>27.227849321043369</v>
       </c>
       <c r="D163" s="36">
-        <v>10.4</v>
+        <v>30.166666666666668</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="29">
-        <v>31601</v>
+        <v>10402</v>
       </c>
       <c r="B164" s="30" t="s">
-        <v>505</v>
+        <v>18</v>
       </c>
       <c r="C164" s="36">
-        <v>13.460132018002517</v>
+        <v>26.769607654622558</v>
       </c>
       <c r="D164" s="36">
-        <v>25.099999999999998</v>
+        <v>44.300000000000004</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="29">
-        <v>31602</v>
+        <v>30803</v>
       </c>
       <c r="B165" s="30" t="s">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="C165" s="36">
-        <v>158.91903299949041</v>
+        <v>26.756346646297885</v>
       </c>
       <c r="D165" s="36">
-        <v>216.06666666666669</v>
+        <v>16.433333333333334</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="29">
-        <v>40101</v>
+        <v>71503</v>
       </c>
       <c r="B166" s="30" t="s">
-        <v>173</v>
+        <v>261</v>
       </c>
       <c r="C166" s="36">
-        <v>27.227849321043369</v>
+        <v>26.460515411108545</v>
       </c>
       <c r="D166" s="36">
-        <v>30.166666666666668</v>
+        <v>51.633333333333333</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="29">
-        <v>40102</v>
+        <v>50303</v>
       </c>
       <c r="B167" s="30" t="s">
-        <v>174</v>
+        <v>219</v>
       </c>
       <c r="C167" s="36">
-        <v>9.4371418941691942</v>
+        <v>26.352984873547797</v>
       </c>
       <c r="D167" s="36">
-        <v>12.6</v>
+        <v>46.233333333333327</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="29">
-        <v>40103</v>
+        <v>70502</v>
       </c>
       <c r="B168" s="30" t="s">
-        <v>175</v>
+        <v>279</v>
       </c>
       <c r="C168" s="36">
-        <v>0</v>
+        <v>26.111121272759434</v>
       </c>
       <c r="D168" s="36">
-        <v>19.266666666666666</v>
+        <v>38.333333333333336</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="29">
-        <v>40104</v>
+        <v>40601</v>
       </c>
       <c r="B169" s="30" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C169" s="36">
-        <v>11.799534368021163</v>
+        <v>26.052566062139221</v>
       </c>
       <c r="D169" s="36">
-        <v>8.3333333333333339</v>
+        <v>9.7000000000000011</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="29">
-        <v>40201</v>
+        <v>10303</v>
       </c>
       <c r="B170" s="30" t="s">
-        <v>177</v>
+        <v>367</v>
       </c>
       <c r="C170" s="36">
-        <v>16.468625326827759</v>
+        <v>25.048509503259666</v>
       </c>
       <c r="D170" s="36">
-        <v>21.133333333333333</v>
+        <v>29.833333333333332</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="29">
-        <v>40202</v>
+        <v>50202</v>
       </c>
       <c r="B171" s="30" t="s">
-        <v>508</v>
+        <v>214</v>
       </c>
       <c r="C171" s="36">
-        <v>8.3689011632772612</v>
+        <v>25.048057637625703</v>
       </c>
       <c r="D171" s="36">
-        <v>34.699999999999996</v>
+        <v>18.400000000000002</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="29">
-        <v>40301</v>
+        <v>30703</v>
       </c>
       <c r="B172" s="30" t="s">
-        <v>179</v>
+        <v>477</v>
       </c>
       <c r="C172" s="36">
-        <v>0</v>
+        <v>25.031289111389238</v>
       </c>
       <c r="D172" s="36">
-        <v>13.033333333333333</v>
+        <v>34.233333333333327</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="29">
-        <v>40302</v>
+        <v>50502</v>
       </c>
       <c r="B173" s="30" t="s">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="C173" s="36">
-        <v>0</v>
+        <v>24.907154512806642</v>
       </c>
       <c r="D173" s="36">
-        <v>68.466666666666669</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="29">
-        <v>40401</v>
+        <v>30301</v>
       </c>
       <c r="B174" s="30" t="s">
-        <v>509</v>
+        <v>464</v>
       </c>
       <c r="C174" s="36">
-        <v>5.0735667174023344</v>
+        <v>24.522721483327231</v>
       </c>
       <c r="D174" s="36">
-        <v>63.033333333333331</v>
+        <v>35.666666666666664</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="29">
-        <v>40402</v>
+        <v>30802</v>
       </c>
       <c r="B175" s="30" t="s">
-        <v>182</v>
+        <v>479</v>
       </c>
       <c r="C175" s="36">
-        <v>15.290527708426689</v>
+        <v>24.393708206615816</v>
       </c>
       <c r="D175" s="36">
-        <v>0</v>
+        <v>29.600000000000005</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="29">
-        <v>40501</v>
+        <v>60402</v>
       </c>
       <c r="B176" s="30" t="s">
-        <v>183</v>
+        <v>528</v>
       </c>
       <c r="C176" s="36">
-        <v>14.324595330181923</v>
+        <v>23.910929644391711</v>
       </c>
       <c r="D176" s="36">
-        <v>0</v>
+        <v>17.633333333333333</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="29">
-        <v>40502</v>
+        <v>20202</v>
       </c>
       <c r="B177" s="30" t="s">
-        <v>184</v>
+        <v>380</v>
       </c>
       <c r="C177" s="36">
-        <v>0</v>
+        <v>23.856326375743411</v>
       </c>
       <c r="D177" s="36">
-        <v>0</v>
+        <v>17.666666666666668</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="29">
-        <v>40503</v>
+        <v>30203</v>
       </c>
       <c r="B178" s="30" t="s">
-        <v>185</v>
+        <v>463</v>
       </c>
       <c r="C178" s="36">
-        <v>0</v>
+        <v>23.813315929731875</v>
       </c>
       <c r="D178" s="36">
-        <v>0</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="29">
-        <v>40504</v>
+        <v>30903</v>
       </c>
       <c r="B179" s="30" t="s">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="C179" s="36">
-        <v>0</v>
+        <v>23.808336547770903</v>
       </c>
       <c r="D179" s="36">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="29">
-        <v>40505</v>
+        <v>71301</v>
       </c>
       <c r="B180" s="30" t="s">
-        <v>187</v>
+        <v>312</v>
       </c>
       <c r="C180" s="36">
-        <v>0</v>
+        <v>23.572097441245337</v>
       </c>
       <c r="D180" s="36">
-        <v>0</v>
+        <v>36.666666666666664</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="29">
-        <v>40601</v>
+        <v>30905</v>
       </c>
       <c r="B181" s="30" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="C181" s="36">
-        <v>26.052566062139221</v>
+        <v>23.396648984812416</v>
       </c>
       <c r="D181" s="36">
-        <v>9.7000000000000011</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="29">
-        <v>40602</v>
+        <v>80301</v>
       </c>
       <c r="B182" s="30" t="s">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="C182" s="36">
-        <v>9.2387287509238725</v>
+        <v>23.242507079703188</v>
       </c>
       <c r="D182" s="36">
-        <v>0</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="29">
-        <v>40603</v>
+        <v>20501</v>
       </c>
       <c r="B183" s="30" t="s">
-        <v>190</v>
+        <v>398</v>
       </c>
       <c r="C183" s="36">
-        <v>0</v>
+        <v>23.177651761447567</v>
       </c>
       <c r="D183" s="36">
-        <v>0</v>
+        <v>16.866666666666667</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="29">
-        <v>40701</v>
+        <v>20404</v>
       </c>
       <c r="B184" s="30" t="s">
-        <v>191</v>
+        <v>396</v>
       </c>
       <c r="C184" s="36">
-        <v>62.887958163078423</v>
+        <v>22.967480788226933</v>
       </c>
       <c r="D184" s="36">
-        <v>54.666666666666664</v>
+        <v>9.8666666666666654</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="29">
-        <v>40702</v>
+        <v>21201</v>
       </c>
       <c r="B185" s="30" t="s">
-        <v>192</v>
+        <v>434</v>
       </c>
       <c r="C185" s="36">
-        <v>19.972039145196725</v>
+        <v>22.87855304905834</v>
       </c>
       <c r="D185" s="36">
-        <v>29.033333333333331</v>
+        <v>32.266666666666666</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="29">
-        <v>40801</v>
+        <v>30402</v>
       </c>
       <c r="B186" s="30" t="s">
-        <v>512</v>
+        <v>468</v>
       </c>
       <c r="C186" s="36">
-        <v>5.2931057297869524</v>
+        <v>22.331737100336895</v>
       </c>
       <c r="D186" s="36">
-        <v>6.833333333333333</v>
+        <v>32.333333333333336</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="29">
-        <v>40802</v>
+        <v>21602</v>
       </c>
       <c r="B187" s="30" t="s">
-        <v>194</v>
+        <v>450</v>
       </c>
       <c r="C187" s="36">
-        <v>0</v>
+        <v>22.14833355481667</v>
       </c>
       <c r="D187" s="36">
         <v>0</v>
@@ -43192,13 +43192,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="29">
-        <v>40901</v>
+        <v>51401</v>
       </c>
       <c r="B188" s="30" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="C188" s="36">
-        <v>0</v>
+        <v>22.002200220022004</v>
       </c>
       <c r="D188" s="36">
         <v>0</v>
@@ -43206,1343 +43206,1343 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="29">
-        <v>40902</v>
+        <v>90402</v>
       </c>
       <c r="B189" s="30" t="s">
-        <v>196</v>
+        <v>552</v>
       </c>
       <c r="C189" s="36">
-        <v>0</v>
+        <v>21.753317380900587</v>
       </c>
       <c r="D189" s="36">
-        <v>0</v>
+        <v>38.766666666666666</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="29">
-        <v>40903</v>
+        <v>20301</v>
       </c>
       <c r="B190" s="30" t="s">
-        <v>197</v>
+        <v>385</v>
       </c>
       <c r="C190" s="36">
-        <v>0</v>
+        <v>21.13492945404413</v>
       </c>
       <c r="D190" s="36">
-        <v>0</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="29">
-        <v>41001</v>
+        <v>51204</v>
       </c>
       <c r="B191" s="30" t="s">
-        <v>198</v>
+        <v>525</v>
       </c>
       <c r="C191" s="36">
-        <v>6.2709685510927153</v>
+        <v>21.042584025373767</v>
       </c>
       <c r="D191" s="36">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="29">
-        <v>41101</v>
+        <v>20802</v>
       </c>
       <c r="B192" s="30" t="s">
-        <v>199</v>
+        <v>412</v>
       </c>
       <c r="C192" s="36">
-        <v>11.96124688614576</v>
+        <v>20.521079953911396</v>
       </c>
       <c r="D192" s="36">
-        <v>13.166666666666666</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="29">
-        <v>41201</v>
+        <v>50302</v>
       </c>
       <c r="B193" s="30" t="s">
-        <v>200</v>
+        <v>520</v>
       </c>
       <c r="C193" s="36">
-        <v>4.8562548562548562</v>
+        <v>20.181634712411704</v>
       </c>
       <c r="D193" s="36">
-        <v>15.733333333333334</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="29">
-        <v>41202</v>
+        <v>20901</v>
       </c>
       <c r="B194" s="30" t="s">
-        <v>513</v>
+        <v>418</v>
       </c>
       <c r="C194" s="36">
-        <v>0</v>
+        <v>20.046047740199544</v>
       </c>
       <c r="D194" s="36">
-        <v>44.766666666666673</v>
+        <v>65.366666666666674</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="29">
-        <v>41301</v>
+        <v>21002</v>
       </c>
       <c r="B195" s="30" t="s">
-        <v>202</v>
+        <v>424</v>
       </c>
       <c r="C195" s="36">
-        <v>0</v>
+        <v>19.975164068130518</v>
       </c>
       <c r="D195" s="36">
-        <v>0</v>
+        <v>35.199999999999996</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="29">
-        <v>41401</v>
+        <v>40702</v>
       </c>
       <c r="B196" s="30" t="s">
-        <v>514</v>
+        <v>192</v>
       </c>
       <c r="C196" s="36">
-        <v>2.5342760840365952</v>
+        <v>19.972039145196725</v>
       </c>
       <c r="D196" s="36">
-        <v>3.3666666666666667</v>
+        <v>29.033333333333331</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="29">
-        <v>41501</v>
+        <v>10502</v>
       </c>
       <c r="B197" s="30" t="s">
-        <v>204</v>
+        <v>369</v>
       </c>
       <c r="C197" s="36">
-        <v>0</v>
+        <v>19.916942113738454</v>
       </c>
       <c r="D197" s="36">
-        <v>0</v>
+        <v>20.233333333333334</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="29">
-        <v>41502</v>
+        <v>50701</v>
       </c>
       <c r="B198" s="30" t="s">
-        <v>515</v>
+        <v>228</v>
       </c>
       <c r="C198" s="36">
-        <v>0</v>
+        <v>19.70885849431065</v>
       </c>
       <c r="D198" s="36">
-        <v>0</v>
+        <v>8.2000000000000011</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="29">
-        <v>41503</v>
+        <v>21203</v>
       </c>
       <c r="B199" s="30" t="s">
-        <v>206</v>
+        <v>436</v>
       </c>
       <c r="C199" s="36">
-        <v>0</v>
+        <v>19.358460356025745</v>
       </c>
       <c r="D199" s="36">
-        <v>0</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="29">
-        <v>41601</v>
+        <v>50702</v>
       </c>
       <c r="B200" s="30" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="C200" s="36">
-        <v>4.9258657209004477</v>
+        <v>18.801908576426573</v>
       </c>
       <c r="D200" s="36">
-        <v>13.799999999999999</v>
+        <v>14.633333333333333</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="29">
-        <v>50101</v>
+        <v>31201</v>
       </c>
       <c r="B201" s="30" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C201" s="36">
-        <v>39.288922384088487</v>
+        <v>18.721746579771555</v>
       </c>
       <c r="D201" s="36">
-        <v>50.433333333333337</v>
+        <v>20.866666666666667</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="29">
-        <v>50102</v>
+        <v>51201</v>
       </c>
       <c r="B202" s="30" t="s">
-        <v>516</v>
+        <v>240</v>
       </c>
       <c r="C202" s="36">
-        <v>5.3879943585825947</v>
+        <v>18.603830706391413</v>
       </c>
       <c r="D202" s="36">
-        <v>8.6666666666666661</v>
+        <v>13.199999999999998</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="29">
-        <v>50103</v>
+        <v>20102</v>
       </c>
       <c r="B203" s="30" t="s">
-        <v>211</v>
+        <v>375</v>
       </c>
       <c r="C203" s="36">
-        <v>28.103945274208328</v>
+        <v>18.519485543839171</v>
       </c>
       <c r="D203" s="36">
-        <v>30.233333333333331</v>
+        <v>91.266666666666666</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="29">
-        <v>50104</v>
+        <v>30201</v>
       </c>
       <c r="B204" s="30" t="s">
-        <v>517</v>
+        <v>461</v>
       </c>
       <c r="C204" s="36">
-        <v>12.059816690786299</v>
+        <v>18.349234179078731</v>
       </c>
       <c r="D204" s="36">
-        <v>49.199999999999996</v>
+        <v>28.366666666666664</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="29">
-        <v>50201</v>
+        <v>31101</v>
       </c>
       <c r="B205" s="30" t="s">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="C205" s="36">
-        <v>45.938166229086335</v>
+        <v>18.242665665561393</v>
       </c>
       <c r="D205" s="36">
-        <v>12.866666666666667</v>
+        <v>20.566666666666666</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="29">
-        <v>50202</v>
+        <v>70704</v>
       </c>
       <c r="B206" s="30" t="s">
-        <v>214</v>
+        <v>287</v>
       </c>
       <c r="C206" s="36">
-        <v>25.048057637625703</v>
+        <v>18.096272167933407</v>
       </c>
       <c r="D206" s="36">
-        <v>18.400000000000002</v>
+        <v>33.166666666666664</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="29">
-        <v>50203</v>
+        <v>31405</v>
       </c>
       <c r="B207" s="30" t="s">
-        <v>215</v>
+        <v>503</v>
       </c>
       <c r="C207" s="36">
-        <v>67.185191953962018</v>
+        <v>17.940437746681017</v>
       </c>
       <c r="D207" s="36">
-        <v>45.599999999999994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="29">
-        <v>50204</v>
+        <v>80303</v>
       </c>
       <c r="B208" s="30" t="s">
-        <v>519</v>
+        <v>325</v>
       </c>
       <c r="C208" s="36">
-        <v>44.931449145075014</v>
+        <v>17.89034991713255</v>
       </c>
       <c r="D208" s="36">
-        <v>88.466666666666654</v>
+        <v>31.866666666666664</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="29">
-        <v>50301</v>
+        <v>50403</v>
       </c>
       <c r="B209" s="30" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C209" s="36">
-        <v>14.09436993456805</v>
+        <v>17.255400733697076</v>
       </c>
       <c r="D209" s="36">
-        <v>26.433333333333334</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="29">
-        <v>50302</v>
+        <v>21301</v>
       </c>
       <c r="B210" s="30" t="s">
-        <v>520</v>
+        <v>438</v>
       </c>
       <c r="C210" s="36">
-        <v>20.181634712411704</v>
+        <v>16.578410405949786</v>
       </c>
       <c r="D210" s="36">
-        <v>34.200000000000003</v>
+        <v>19.566666666666666</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="29">
-        <v>50303</v>
+        <v>40201</v>
       </c>
       <c r="B211" s="30" t="s">
-        <v>219</v>
+        <v>177</v>
       </c>
       <c r="C211" s="36">
-        <v>26.352984873547797</v>
+        <v>16.468625326827759</v>
       </c>
       <c r="D211" s="36">
-        <v>46.233333333333327</v>
+        <v>21.133333333333333</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="29">
-        <v>50401</v>
+        <v>10304</v>
       </c>
       <c r="B212" s="30" t="s">
-        <v>220</v>
+        <v>16</v>
       </c>
       <c r="C212" s="36">
-        <v>15.352146571253156</v>
+        <v>16.105698736805746</v>
       </c>
       <c r="D212" s="36">
-        <v>10.133333333333335</v>
+        <v>53.966666666666661</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="29">
-        <v>50402</v>
+        <v>70705</v>
       </c>
       <c r="B213" s="30" t="s">
-        <v>221</v>
+        <v>288</v>
       </c>
       <c r="C213" s="36">
-        <v>11.172199736813958</v>
+        <v>15.796019959968428</v>
       </c>
       <c r="D213" s="36">
-        <v>16.366666666666667</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="29">
-        <v>50403</v>
+        <v>31002</v>
       </c>
       <c r="B214" s="30" t="s">
-        <v>222</v>
+        <v>487</v>
       </c>
       <c r="C214" s="36">
-        <v>17.255400733697076</v>
+        <v>15.485122623131119</v>
       </c>
       <c r="D214" s="36">
-        <v>14.4</v>
+        <v>29.833333333333332</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="29">
-        <v>50404</v>
+        <v>50401</v>
       </c>
       <c r="B215" s="30" t="s">
-        <v>521</v>
+        <v>220</v>
       </c>
       <c r="C215" s="36">
-        <v>30.718658903726382</v>
+        <v>15.352146571253156</v>
       </c>
       <c r="D215" s="36">
-        <v>32.699999999999996</v>
+        <v>10.133333333333335</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="29">
-        <v>50405</v>
+        <v>50801</v>
       </c>
       <c r="B216" s="30" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="C216" s="36">
-        <v>0</v>
+        <v>15.318627450980392</v>
       </c>
       <c r="D216" s="36">
-        <v>3.0333333333333332</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="29">
-        <v>50501</v>
+        <v>40402</v>
       </c>
       <c r="B217" s="30" t="s">
-        <v>304</v>
+        <v>182</v>
       </c>
       <c r="C217" s="36">
-        <v>0</v>
+        <v>15.290527708426689</v>
       </c>
       <c r="D217" s="36">
-        <v>4.333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="29">
-        <v>50502</v>
+        <v>20904</v>
       </c>
       <c r="B218" s="30" t="s">
-        <v>225</v>
+        <v>421</v>
       </c>
       <c r="C218" s="36">
-        <v>24.907154512806642</v>
+        <v>14.872305567630548</v>
       </c>
       <c r="D218" s="36">
-        <v>18.7</v>
+        <v>10.833333333333334</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="29">
-        <v>50601</v>
+        <v>21307</v>
       </c>
       <c r="B219" s="30" t="s">
-        <v>226</v>
+        <v>444</v>
       </c>
       <c r="C219" s="36">
-        <v>47.363232260126516</v>
+        <v>14.703712253182355</v>
       </c>
       <c r="D219" s="36">
-        <v>65.933333333333337</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="29">
-        <v>50602</v>
+        <v>20801</v>
       </c>
       <c r="B220" s="30" t="s">
-        <v>522</v>
+        <v>411</v>
       </c>
       <c r="C220" s="36">
-        <v>46.572575636112255</v>
+        <v>14.575271881732673</v>
       </c>
       <c r="D220" s="36">
-        <v>25.566666666666663</v>
+        <v>56.866666666666667</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="29">
-        <v>50701</v>
+        <v>10602</v>
       </c>
       <c r="B221" s="30" t="s">
-        <v>228</v>
+        <v>370</v>
       </c>
       <c r="C221" s="36">
-        <v>19.70885849431065</v>
+        <v>14.357462895918644</v>
       </c>
       <c r="D221" s="36">
-        <v>8.2000000000000011</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="29">
-        <v>50702</v>
+        <v>40501</v>
       </c>
       <c r="B222" s="30" t="s">
-        <v>229</v>
+        <v>183</v>
       </c>
       <c r="C222" s="36">
-        <v>18.801908576426573</v>
+        <v>14.324595330181923</v>
       </c>
       <c r="D222" s="36">
-        <v>14.633333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="29">
-        <v>50801</v>
+        <v>30601</v>
       </c>
       <c r="B223" s="30" t="s">
-        <v>230</v>
+        <v>473</v>
       </c>
       <c r="C223" s="36">
-        <v>15.318627450980392</v>
+        <v>14.319320579371373</v>
       </c>
       <c r="D223" s="36">
-        <v>61.4</v>
+        <v>16.733333333333334</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="29">
-        <v>50802</v>
+        <v>71302</v>
       </c>
       <c r="B224" s="30" t="s">
-        <v>231</v>
+        <v>313</v>
       </c>
       <c r="C224" s="36">
-        <v>45.396801580733957</v>
+        <v>14.235236004987131</v>
       </c>
       <c r="D224" s="36">
-        <v>36.200000000000003</v>
+        <v>31.933333333333337</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="29">
-        <v>50901</v>
+        <v>50301</v>
       </c>
       <c r="B225" s="30" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C225" s="36">
-        <v>48.197227734106747</v>
+        <v>14.09436993456805</v>
       </c>
       <c r="D225" s="36">
-        <v>7.4666666666666659</v>
+        <v>26.433333333333334</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="29">
-        <v>50902</v>
+        <v>20903</v>
       </c>
       <c r="B226" s="30" t="s">
-        <v>233</v>
+        <v>420</v>
       </c>
       <c r="C226" s="36">
-        <v>29.63178005033264</v>
+        <v>14.059356083895016</v>
       </c>
       <c r="D226" s="36">
-        <v>44.933333333333337</v>
+        <v>8.6666666666666661</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="29">
-        <v>51001</v>
+        <v>10401</v>
       </c>
       <c r="B227" s="30" t="s">
-        <v>523</v>
+        <v>17</v>
       </c>
       <c r="C227" s="36">
-        <v>0</v>
+        <v>13.924720239973412</v>
       </c>
       <c r="D227" s="36">
-        <v>0</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="29">
-        <v>51002</v>
+        <v>21305</v>
       </c>
       <c r="B228" s="30" t="s">
-        <v>235</v>
+        <v>442</v>
       </c>
       <c r="C228" s="36">
-        <v>9.2361688371663444</v>
+        <v>13.900323818807957</v>
       </c>
       <c r="D228" s="36">
-        <v>0</v>
+        <v>32.866666666666667</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="29">
-        <v>51003</v>
+        <v>20104</v>
       </c>
       <c r="B229" s="30" t="s">
-        <v>524</v>
+        <v>377</v>
       </c>
       <c r="C229" s="36">
-        <v>0</v>
+        <v>13.873717008348869</v>
       </c>
       <c r="D229" s="36">
-        <v>0</v>
+        <v>93.033333333333346</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="29">
-        <v>51101</v>
+        <v>80601</v>
       </c>
       <c r="B230" s="30" t="s">
-        <v>237</v>
+        <v>330</v>
       </c>
       <c r="C230" s="36">
-        <v>0</v>
+        <v>13.468013468013467</v>
       </c>
       <c r="D230" s="36">
-        <v>8.3666666666666671</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="29">
-        <v>51102</v>
+        <v>31601</v>
       </c>
       <c r="B231" s="30" t="s">
-        <v>238</v>
+        <v>505</v>
       </c>
       <c r="C231" s="36">
-        <v>27.830858921333164</v>
+        <v>13.460132018002517</v>
       </c>
       <c r="D231" s="36">
-        <v>63.066666666666663</v>
+        <v>25.099999999999998</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="29">
-        <v>51103</v>
+        <v>10801</v>
       </c>
       <c r="B232" s="30" t="s">
-        <v>239</v>
+        <v>30</v>
       </c>
       <c r="C232" s="36">
-        <v>52.721380838268381</v>
+        <v>13.284446569955897</v>
       </c>
       <c r="D232" s="36">
-        <v>18.633333333333336</v>
+        <v>26.100000000000005</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="29">
-        <v>51201</v>
+        <v>70904</v>
       </c>
       <c r="B233" s="30" t="s">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="C233" s="36">
-        <v>18.603830706391413</v>
+        <v>12.950012950012949</v>
       </c>
       <c r="D233" s="36">
-        <v>13.199999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="29">
-        <v>51202</v>
+        <v>20402</v>
       </c>
       <c r="B234" s="30" t="s">
-        <v>241</v>
+        <v>394</v>
       </c>
       <c r="C234" s="36">
-        <v>8.5063498001174391</v>
+        <v>12.612966050083253</v>
       </c>
       <c r="D234" s="36">
-        <v>17.599999999999998</v>
+        <v>20.033333333333335</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="29">
-        <v>51203</v>
+        <v>60502</v>
       </c>
       <c r="B235" s="30" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="C235" s="36">
-        <v>11.652460167880498</v>
+        <v>12.524469953064388</v>
       </c>
       <c r="D235" s="36">
-        <v>42.199999999999996</v>
+        <v>5.666666666666667</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="29">
-        <v>51204</v>
+        <v>20803</v>
       </c>
       <c r="B236" s="30" t="s">
-        <v>525</v>
+        <v>413</v>
       </c>
       <c r="C236" s="36">
-        <v>21.042584025373767</v>
+        <v>12.331888292981178</v>
       </c>
       <c r="D236" s="36">
-        <v>17</v>
+        <v>30.733333333333334</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="29">
-        <v>51301</v>
+        <v>50104</v>
       </c>
       <c r="B237" s="30" t="s">
-        <v>243</v>
+        <v>517</v>
       </c>
       <c r="C237" s="36">
-        <v>46.554981456369291</v>
+        <v>12.059816690786299</v>
       </c>
       <c r="D237" s="36">
-        <v>0</v>
+        <v>49.199999999999996</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="29">
-        <v>51302</v>
+        <v>41101</v>
       </c>
       <c r="B238" s="30" t="s">
-        <v>244</v>
+        <v>199</v>
       </c>
       <c r="C238" s="36">
-        <v>0</v>
+        <v>11.96124688614576</v>
       </c>
       <c r="D238" s="36">
-        <v>11.866666666666667</v>
+        <v>13.166666666666666</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="29">
-        <v>51401</v>
+        <v>60401</v>
       </c>
       <c r="B239" s="30" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C239" s="36">
-        <v>22.002200220022004</v>
+        <v>11.833034373828276</v>
       </c>
       <c r="D239" s="36">
-        <v>0</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="29">
-        <v>51402</v>
+        <v>20401</v>
       </c>
       <c r="B240" s="30" t="s">
-        <v>246</v>
+        <v>393</v>
       </c>
       <c r="C240" s="36">
-        <v>28.851975044571049</v>
+        <v>11.810252179432171</v>
       </c>
       <c r="D240" s="36">
-        <v>0</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="29">
-        <v>51501</v>
+        <v>40104</v>
       </c>
       <c r="B241" s="30" t="s">
-        <v>247</v>
+        <v>507</v>
       </c>
       <c r="C241" s="36">
-        <v>0</v>
+        <v>11.799534368021163</v>
       </c>
       <c r="D241" s="36">
-        <v>29.433333333333334</v>
+        <v>8.3333333333333339</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="29">
-        <v>51601</v>
+        <v>51203</v>
       </c>
       <c r="B242" s="30" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C242" s="36">
-        <v>0</v>
+        <v>11.652460167880498</v>
       </c>
       <c r="D242" s="36">
-        <v>0</v>
+        <v>42.199999999999996</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="29">
-        <v>60101</v>
+        <v>11003</v>
       </c>
       <c r="B243" s="30" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="C243" s="36">
-        <v>39.306624979784942</v>
+        <v>11.42026568222971</v>
       </c>
       <c r="D243" s="36">
-        <v>49.166666666666664</v>
+        <v>74.600000000000009</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="29">
-        <v>60201</v>
+        <v>10202</v>
       </c>
       <c r="B244" s="30" t="s">
-        <v>253</v>
+        <v>12</v>
       </c>
       <c r="C244" s="36">
-        <v>33.476683093558798</v>
+        <v>11.385580207384047</v>
       </c>
       <c r="D244" s="36">
-        <v>20.866666666666664</v>
+        <v>24</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="29">
-        <v>60202</v>
+        <v>21004</v>
       </c>
       <c r="B245" s="30" t="s">
-        <v>254</v>
+        <v>426</v>
       </c>
       <c r="C245" s="36">
-        <v>121.11815105301442</v>
+        <v>11.28924042075637</v>
       </c>
       <c r="D245" s="36">
-        <v>84.233333333333334</v>
+        <v>1.9333333333333333</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="29">
-        <v>60301</v>
+        <v>50402</v>
       </c>
       <c r="B246" s="30" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="C246" s="36">
-        <v>96.2721456873699</v>
+        <v>11.172199736813958</v>
       </c>
       <c r="D246" s="36">
-        <v>120.83333333333333</v>
+        <v>16.366666666666667</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="29">
-        <v>60302</v>
+        <v>20305</v>
       </c>
       <c r="B247" s="30" t="s">
-        <v>526</v>
+        <v>389</v>
       </c>
       <c r="C247" s="36">
-        <v>82.595915539894563</v>
+        <v>10.918222513374822</v>
       </c>
       <c r="D247" s="36">
-        <v>72.333333333333329</v>
+        <v>14.066666666666668</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="29">
-        <v>60303</v>
+        <v>30502</v>
       </c>
       <c r="B248" s="30" t="s">
-        <v>527</v>
+        <v>472</v>
       </c>
       <c r="C248" s="36">
-        <v>113.49326857512436</v>
+        <v>10.480853099237502</v>
       </c>
       <c r="D248" s="36">
-        <v>75.899999999999991</v>
+        <v>37.033333333333331</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="29">
-        <v>60401</v>
+        <v>20403</v>
       </c>
       <c r="B249" s="30" t="s">
-        <v>258</v>
+        <v>395</v>
       </c>
       <c r="C249" s="36">
-        <v>11.833034373828276</v>
+        <v>10.246232807689848</v>
       </c>
       <c r="D249" s="36">
-        <v>38.5</v>
+        <v>13.666666666666666</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="29">
-        <v>60402</v>
+        <v>21901</v>
       </c>
       <c r="B250" s="30" t="s">
-        <v>528</v>
+        <v>457</v>
       </c>
       <c r="C250" s="36">
-        <v>23.910929644391711</v>
+        <v>10.19936763920637</v>
       </c>
       <c r="D250" s="36">
-        <v>17.633333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="29">
-        <v>60501</v>
+        <v>70804</v>
       </c>
       <c r="B251" s="30" t="s">
-        <v>260</v>
+        <v>532</v>
       </c>
       <c r="C251" s="36">
-        <v>32.678816542882352</v>
+        <v>10.184336490477646</v>
       </c>
       <c r="D251" s="36">
-        <v>46.033333333333339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="29">
-        <v>60502</v>
+        <v>31402</v>
       </c>
       <c r="B252" s="30" t="s">
-        <v>261</v>
+        <v>500</v>
       </c>
       <c r="C252" s="36">
-        <v>12.524469953064388</v>
+        <v>10.111111714811059</v>
       </c>
       <c r="D252" s="36">
-        <v>5.666666666666667</v>
+        <v>74.899999999999991</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="29">
-        <v>60601</v>
+        <v>20204</v>
       </c>
       <c r="B253" s="30" t="s">
-        <v>494</v>
+        <v>382</v>
       </c>
       <c r="C253" s="36">
-        <v>77.510346644155319</v>
+        <v>10.056821735530342</v>
       </c>
       <c r="D253" s="36">
-        <v>32.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="29">
-        <v>70101</v>
+        <v>31501</v>
       </c>
       <c r="B254" s="30" t="s">
-        <v>264</v>
+        <v>504</v>
       </c>
       <c r="C254" s="36">
-        <v>91.920727200143901</v>
+        <v>9.5848476751636227</v>
       </c>
       <c r="D254" s="36">
-        <v>139.76666666666665</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="29">
-        <v>70102</v>
+        <v>40102</v>
       </c>
       <c r="B255" s="30" t="s">
-        <v>265</v>
+        <v>174</v>
       </c>
       <c r="C255" s="36">
-        <v>76.454048372635896</v>
+        <v>9.4371418941691942</v>
       </c>
       <c r="D255" s="36">
-        <v>132.33333333333334</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="29">
-        <v>70103</v>
+        <v>40602</v>
       </c>
       <c r="B256" s="30" t="s">
-        <v>266</v>
+        <v>189</v>
       </c>
       <c r="C256" s="36">
-        <v>30.35983188671122</v>
+        <v>9.2387287509238725</v>
       </c>
       <c r="D256" s="36">
-        <v>68.86666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="29">
-        <v>70104</v>
+        <v>21302</v>
       </c>
       <c r="B257" s="30" t="s">
-        <v>267</v>
+        <v>439</v>
       </c>
       <c r="C257" s="36">
-        <v>85.724482111952668</v>
+        <v>9.2361688371663444</v>
       </c>
       <c r="D257" s="36">
-        <v>148.69999999999999</v>
+        <v>11.633333333333333</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="29">
-        <v>70105</v>
+        <v>51002</v>
       </c>
       <c r="B258" s="30" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="C258" s="36">
-        <v>85.482394630284887</v>
+        <v>9.2361688371663444</v>
       </c>
       <c r="D258" s="36">
-        <v>79.366666666666674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="29">
-        <v>70201</v>
+        <v>30303</v>
       </c>
       <c r="B259" s="30" t="s">
-        <v>269</v>
+        <v>466</v>
       </c>
       <c r="C259" s="36">
-        <v>109.22549099832922</v>
+        <v>9.1411024576170004</v>
       </c>
       <c r="D259" s="36">
-        <v>118.16666666666667</v>
+        <v>3.8000000000000003</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="29">
-        <v>70202</v>
+        <v>80801</v>
       </c>
       <c r="B260" s="30" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="C260" s="36">
-        <v>38.050481019962739</v>
+        <v>9.0130899448678203</v>
       </c>
       <c r="D260" s="36">
-        <v>61.699999999999996</v>
+        <v>27.333333333333332</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="29">
-        <v>70301</v>
+        <v>20605</v>
       </c>
       <c r="B261" s="30" t="s">
-        <v>271</v>
+        <v>405</v>
       </c>
       <c r="C261" s="36">
-        <v>30.335433771763405</v>
+        <v>8.934155275618691</v>
       </c>
       <c r="D261" s="36">
-        <v>40.133333333333333</v>
+        <v>62.033333333333331</v>
       </c>
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="29">
-        <v>70302</v>
+        <v>21701</v>
       </c>
       <c r="B262" s="30" t="s">
-        <v>272</v>
+        <v>451</v>
       </c>
       <c r="C262" s="36">
-        <v>87.937333846640115</v>
+        <v>8.7599664792326504</v>
       </c>
       <c r="D262" s="36">
-        <v>71.233333333333334</v>
+        <v>39.800000000000004</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="29">
-        <v>70303</v>
+        <v>31203</v>
       </c>
       <c r="B263" s="30" t="s">
-        <v>273</v>
+        <v>491</v>
       </c>
       <c r="C263" s="36">
-        <v>4.0665284047009065</v>
+        <v>8.7391062138250746</v>
       </c>
       <c r="D263" s="36">
-        <v>35.800000000000004</v>
+        <v>21.466666666666669</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="29">
-        <v>70401</v>
+        <v>30602</v>
       </c>
       <c r="B264" s="30" t="s">
-        <v>274</v>
+        <v>474</v>
       </c>
       <c r="C264" s="36">
-        <v>76.217952445895548</v>
+        <v>8.6471251595714005</v>
       </c>
       <c r="D264" s="36">
-        <v>71.166666666666671</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="29">
-        <v>70402</v>
+        <v>20304</v>
       </c>
       <c r="B265" s="30" t="s">
-        <v>275</v>
+        <v>388</v>
       </c>
       <c r="C265" s="36">
-        <v>54.900778777965236</v>
+        <v>8.5910652920962196</v>
       </c>
       <c r="D265" s="36">
-        <v>68.899999999999991</v>
+        <v>12.299999999999999</v>
       </c>
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="29">
-        <v>70403</v>
+        <v>51202</v>
       </c>
       <c r="B266" s="30" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
       <c r="C266" s="36">
-        <v>172.92490044349407</v>
+        <v>8.5063498001174391</v>
       </c>
       <c r="D266" s="36">
-        <v>154.1</v>
+        <v>17.599999999999998</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="29">
-        <v>70404</v>
+        <v>40202</v>
       </c>
       <c r="B267" s="30" t="s">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="C267" s="36">
-        <v>54.151105716268866</v>
+        <v>8.3689011632772612</v>
       </c>
       <c r="D267" s="36">
-        <v>45.966666666666669</v>
+        <v>34.699999999999996</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="29">
-        <v>70501</v>
+        <v>30302</v>
       </c>
       <c r="B268" s="30" t="s">
-        <v>530</v>
+        <v>465</v>
       </c>
       <c r="C268" s="36">
-        <v>39.920293720951378</v>
+        <v>8.2827528193260829</v>
       </c>
       <c r="D268" s="36">
-        <v>43.933333333333337</v>
+        <v>9.5333333333333332</v>
       </c>
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="29">
-        <v>70502</v>
+        <v>70801</v>
       </c>
       <c r="B269" s="30" t="s">
-        <v>279</v>
+        <v>531</v>
       </c>
       <c r="C269" s="36">
-        <v>26.111121272759434</v>
+        <v>7.6330003122400401</v>
       </c>
       <c r="D269" s="36">
-        <v>38.333333333333336</v>
+        <v>12.566666666666668</v>
       </c>
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="29">
-        <v>70503</v>
+        <v>90202</v>
       </c>
       <c r="B270" s="30" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="C270" s="36">
-        <v>54.664561462933271</v>
+        <v>7.5159714393085304</v>
       </c>
       <c r="D270" s="36">
-        <v>36.233333333333327</v>
+        <v>18.966666666666665</v>
       </c>
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="29">
-        <v>70601</v>
+        <v>21202</v>
       </c>
       <c r="B271" s="30" t="s">
-        <v>281</v>
+        <v>435</v>
       </c>
       <c r="C271" s="36">
-        <v>28.743371214963862</v>
+        <v>6.9701185033158</v>
       </c>
       <c r="D271" s="36">
-        <v>30</v>
+        <v>20.833333333333332</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="29">
-        <v>70602</v>
+        <v>80402</v>
       </c>
       <c r="B272" s="30" t="s">
-        <v>282</v>
+        <v>328</v>
       </c>
       <c r="C272" s="36">
-        <v>45.839798964581007</v>
+        <v>6.9357747260368994</v>
       </c>
       <c r="D272" s="36">
-        <v>60.833333333333336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="29">
-        <v>70603</v>
+        <v>21306</v>
       </c>
       <c r="B273" s="30" t="s">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="C273" s="36">
-        <v>41.61935625593636</v>
+        <v>6.8131493783001185</v>
       </c>
       <c r="D273" s="36">
-        <v>33.366666666666667</v>
+        <v>20.533333333333331</v>
       </c>
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="29">
-        <v>70701</v>
+        <v>41001</v>
       </c>
       <c r="B274" s="30" t="s">
-        <v>284</v>
+        <v>198</v>
       </c>
       <c r="C274" s="36">
-        <v>5.3222630262387565</v>
+        <v>6.2709685510927153</v>
       </c>
       <c r="D274" s="36">
-        <v>35.300000000000004</v>
+        <v>16</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="29">
-        <v>70702</v>
+        <v>20405</v>
       </c>
       <c r="B275" s="30" t="s">
-        <v>285</v>
+        <v>397</v>
       </c>
       <c r="C275" s="36">
-        <v>48.049724561338543</v>
+        <v>6.2583447225920965</v>
       </c>
       <c r="D275" s="36">
-        <v>28.933333333333337</v>
+        <v>9</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="29">
-        <v>70703</v>
+        <v>31302</v>
       </c>
       <c r="B276" s="30" t="s">
-        <v>286</v>
+        <v>496</v>
       </c>
       <c r="C276" s="36">
-        <v>41.498203907418542</v>
+        <v>6.106124442816145</v>
       </c>
       <c r="D276" s="36">
-        <v>45.699999999999996</v>
+        <v>52.333333333333336</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="29">
-        <v>70704</v>
+        <v>50102</v>
       </c>
       <c r="B277" s="30" t="s">
-        <v>287</v>
+        <v>516</v>
       </c>
       <c r="C277" s="36">
-        <v>18.096272167933407</v>
+        <v>5.3879943585825947</v>
       </c>
       <c r="D277" s="36">
-        <v>33.166666666666664</v>
+        <v>8.6666666666666661</v>
       </c>
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="29">
-        <v>70705</v>
+        <v>70701</v>
       </c>
       <c r="B278" s="30" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C278" s="36">
-        <v>15.796019959968428</v>
+        <v>5.3222630262387565</v>
       </c>
       <c r="D278" s="36">
-        <v>33.4</v>
+        <v>35.300000000000004</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="29">
-        <v>70706</v>
+        <v>40801</v>
       </c>
       <c r="B279" s="30" t="s">
-        <v>289</v>
+        <v>512</v>
       </c>
       <c r="C279" s="36">
-        <v>68.913474092850265</v>
+        <v>5.2931057297869524</v>
       </c>
       <c r="D279" s="36">
-        <v>56.133333333333333</v>
+        <v>6.833333333333333</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="29">
-        <v>70707</v>
+        <v>40401</v>
       </c>
       <c r="B280" s="30" t="s">
-        <v>290</v>
+        <v>509</v>
       </c>
       <c r="C280" s="36">
-        <v>29.72762157843253</v>
+        <v>5.0735667174023344</v>
       </c>
       <c r="D280" s="36">
-        <v>87.433333333333337</v>
+        <v>63.033333333333331</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="29">
-        <v>70801</v>
+        <v>41601</v>
       </c>
       <c r="B281" s="30" t="s">
-        <v>531</v>
+        <v>207</v>
       </c>
       <c r="C281" s="36">
-        <v>7.6330003122400401</v>
+        <v>4.9258657209004477</v>
       </c>
       <c r="D281" s="36">
-        <v>12.566666666666668</v>
+        <v>13.799999999999999</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282" s="29">
-        <v>70802</v>
+        <v>41201</v>
       </c>
       <c r="B282" s="30" t="s">
-        <v>292</v>
+        <v>200</v>
       </c>
       <c r="C282" s="36">
-        <v>0</v>
+        <v>4.8562548562548562</v>
       </c>
       <c r="D282" s="36">
-        <v>21.433333333333334</v>
+        <v>15.733333333333334</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283" s="29">
-        <v>70803</v>
+        <v>21703</v>
       </c>
       <c r="B283" s="30" t="s">
-        <v>293</v>
+        <v>453</v>
       </c>
       <c r="C283" s="36">
-        <v>0</v>
+        <v>4.5749839875560427</v>
       </c>
       <c r="D283" s="36">
-        <v>13</v>
+        <v>36.300000000000004</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" s="29">
-        <v>70804</v>
+        <v>20203</v>
       </c>
       <c r="B284" s="30" t="s">
-        <v>532</v>
+        <v>381</v>
       </c>
       <c r="C284" s="36">
-        <v>10.184336490477646</v>
+        <v>4.43675407072186</v>
       </c>
       <c r="D284" s="36">
         <v>0</v>
@@ -44550,489 +44550,489 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="29">
-        <v>70805</v>
+        <v>20804</v>
       </c>
       <c r="B285" s="30" t="s">
-        <v>533</v>
+        <v>414</v>
       </c>
       <c r="C285" s="36">
-        <v>0</v>
+        <v>4.3504742016879847</v>
       </c>
       <c r="D285" s="36">
-        <v>0</v>
+        <v>22.333333333333332</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="29">
-        <v>70901</v>
+        <v>21802</v>
       </c>
       <c r="B286" s="30" t="s">
-        <v>296</v>
+        <v>455</v>
       </c>
       <c r="C286" s="36">
-        <v>28.894956186204894</v>
+        <v>4.2977479800584497</v>
       </c>
       <c r="D286" s="36">
-        <v>43.733333333333327</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287" s="29">
-        <v>70902</v>
+        <v>21303</v>
       </c>
       <c r="B287" s="30" t="s">
-        <v>297</v>
+        <v>440</v>
       </c>
       <c r="C287" s="36">
-        <v>48.729633244673494</v>
+        <v>4.274600324869624</v>
       </c>
       <c r="D287" s="36">
-        <v>53.800000000000004</v>
+        <v>19.900000000000002</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="29">
-        <v>70903</v>
+        <v>21005</v>
       </c>
       <c r="B288" s="30" t="s">
-        <v>298</v>
+        <v>427</v>
       </c>
       <c r="C288" s="36">
-        <v>57.574855237580927</v>
+        <v>4.2625745950554128</v>
       </c>
       <c r="D288" s="36">
-        <v>33.06666666666667</v>
+        <v>9.7999999999999989</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="29">
-        <v>70904</v>
+        <v>70303</v>
       </c>
       <c r="B289" s="30" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="C289" s="36">
-        <v>12.950012950012949</v>
+        <v>4.0665284047009065</v>
       </c>
       <c r="D289" s="36">
-        <v>0</v>
+        <v>35.800000000000004</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" s="29">
-        <v>71001</v>
+        <v>20805</v>
       </c>
       <c r="B290" s="30" t="s">
-        <v>300</v>
+        <v>415</v>
       </c>
       <c r="C290" s="36">
-        <v>112.69900946488991</v>
+        <v>3.8202204267186217</v>
       </c>
       <c r="D290" s="36">
-        <v>226.9666666666667</v>
+        <v>11.133333333333333</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291" s="29">
-        <v>71002</v>
+        <v>71105</v>
       </c>
       <c r="B291" s="30" t="s">
-        <v>534</v>
+        <v>309</v>
       </c>
       <c r="C291" s="36">
-        <v>54.693719583428468</v>
+        <v>3.6799882240376829</v>
       </c>
       <c r="D291" s="36">
-        <v>58.733333333333327</v>
+        <v>33.300000000000004</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292" s="29">
-        <v>71003</v>
+        <v>30501</v>
       </c>
       <c r="B292" s="30" t="s">
-        <v>302</v>
+        <v>471</v>
       </c>
       <c r="C292" s="36">
-        <v>58.663047991285538</v>
+        <v>3.333666700003334</v>
       </c>
       <c r="D292" s="36">
-        <v>95.566666666666677</v>
+        <v>32.233333333333327</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293" s="29">
-        <v>71004</v>
+        <v>41401</v>
       </c>
       <c r="B293" s="30" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="C293" s="36">
-        <v>68.111893122304522</v>
+        <v>2.5342760840365952</v>
       </c>
       <c r="D293" s="36">
-        <v>95.033333333333346</v>
+        <v>3.3666666666666667</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" s="29">
-        <v>71005</v>
+        <v>10404</v>
       </c>
       <c r="B294" s="30" t="s">
-        <v>304</v>
+        <v>368</v>
       </c>
       <c r="C294" s="36">
-        <v>62.469063006639708</v>
+        <v>0</v>
       </c>
       <c r="D294" s="36">
-        <v>88.066666666666677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" s="29">
-        <v>71101</v>
+        <v>10405</v>
       </c>
       <c r="B295" s="30" t="s">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="C295" s="36">
-        <v>28.120551419240041</v>
+        <v>0</v>
       </c>
       <c r="D295" s="36">
-        <v>42.466666666666669</v>
+        <v>8.3333333333333339</v>
       </c>
     </row>
     <row r="296" spans="1:4">
       <c r="A296" s="29">
-        <v>71102</v>
+        <v>11002</v>
       </c>
       <c r="B296" s="30" t="s">
-        <v>306</v>
+        <v>372</v>
       </c>
       <c r="C296" s="36">
-        <v>34.737295069339176</v>
+        <v>0</v>
       </c>
       <c r="D296" s="36">
-        <v>22.7</v>
+        <v>66.733333333333334</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297" s="29">
-        <v>71103</v>
+        <v>20206</v>
       </c>
       <c r="B297" s="30" t="s">
-        <v>307</v>
+        <v>384</v>
       </c>
       <c r="C297" s="36">
-        <v>41.840631450434287</v>
+        <v>0</v>
       </c>
       <c r="D297" s="36">
-        <v>71.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298" s="29">
-        <v>71104</v>
+        <v>20302</v>
       </c>
       <c r="B298" s="30" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="C298" s="36">
-        <v>76.776058127348406</v>
+        <v>0</v>
       </c>
       <c r="D298" s="36">
-        <v>97.166666666666671</v>
+        <v>9.3000000000000007</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" s="29">
-        <v>71105</v>
+        <v>20306</v>
       </c>
       <c r="B299" s="30" t="s">
-        <v>309</v>
+        <v>390</v>
       </c>
       <c r="C299" s="36">
-        <v>3.6799882240376829</v>
+        <v>0</v>
       </c>
       <c r="D299" s="36">
-        <v>33.300000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300" s="29">
-        <v>71106</v>
+        <v>20307</v>
       </c>
       <c r="B300" s="30" t="s">
-        <v>310</v>
+        <v>391</v>
       </c>
       <c r="C300" s="36">
-        <v>79.403606249658523</v>
+        <v>0</v>
       </c>
       <c r="D300" s="36">
-        <v>94.899999999999991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" s="29">
-        <v>71201</v>
+        <v>21204</v>
       </c>
       <c r="B301" s="30" t="s">
-        <v>536</v>
+        <v>437</v>
       </c>
       <c r="C301" s="36">
-        <v>51.305787731609655</v>
+        <v>0</v>
       </c>
       <c r="D301" s="36">
-        <v>33.266666666666673</v>
+        <v>17.400000000000002</v>
       </c>
     </row>
     <row r="302" spans="1:4">
       <c r="A302" s="29">
-        <v>71301</v>
+        <v>21803</v>
       </c>
       <c r="B302" s="30" t="s">
-        <v>312</v>
+        <v>456</v>
       </c>
       <c r="C302" s="36">
-        <v>23.572097441245337</v>
+        <v>0</v>
       </c>
       <c r="D302" s="36">
-        <v>36.666666666666664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303" spans="1:4">
       <c r="A303" s="29">
-        <v>71302</v>
+        <v>21902</v>
       </c>
       <c r="B303" s="30" t="s">
-        <v>313</v>
+        <v>458</v>
       </c>
       <c r="C303" s="36">
-        <v>14.235236004987131</v>
+        <v>0</v>
       </c>
       <c r="D303" s="36">
-        <v>31.933333333333337</v>
+        <v>19.633333333333333</v>
       </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" s="29">
-        <v>71401</v>
+        <v>30202</v>
       </c>
       <c r="B304" s="30" t="s">
-        <v>537</v>
+        <v>462</v>
       </c>
       <c r="C304" s="36">
-        <v>68.581038350585018</v>
+        <v>0</v>
       </c>
       <c r="D304" s="36">
-        <v>67.533333333333346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305" spans="1:4">
       <c r="A305" s="29">
-        <v>71402</v>
+        <v>30404</v>
       </c>
       <c r="B305" s="30" t="s">
-        <v>315</v>
+        <v>470</v>
       </c>
       <c r="C305" s="36">
-        <v>116.98729902377134</v>
+        <v>0</v>
       </c>
       <c r="D305" s="36">
-        <v>125.66666666666667</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="306" spans="1:4">
       <c r="A306" s="29">
-        <v>71403</v>
+        <v>31303</v>
       </c>
       <c r="B306" s="30" t="s">
-        <v>538</v>
+        <v>497</v>
       </c>
       <c r="C306" s="36">
-        <v>37.839357064572937</v>
+        <v>0</v>
       </c>
       <c r="D306" s="36">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" s="29">
-        <v>71501</v>
+        <v>31304</v>
       </c>
       <c r="B307" s="30" t="s">
-        <v>539</v>
+        <v>498</v>
       </c>
       <c r="C307" s="36">
-        <v>61.028728452556805</v>
+        <v>0</v>
       </c>
       <c r="D307" s="36">
-        <v>80.600000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308" spans="1:4">
       <c r="A308" s="29">
-        <v>71502</v>
+        <v>31404</v>
       </c>
       <c r="B308" s="30" t="s">
-        <v>318</v>
+        <v>502</v>
       </c>
       <c r="C308" s="36">
-        <v>117.96212307504335</v>
+        <v>0</v>
       </c>
       <c r="D308" s="36">
-        <v>69.600000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309" s="29">
-        <v>71503</v>
+        <v>40103</v>
       </c>
       <c r="B309" s="30" t="s">
-        <v>261</v>
+        <v>175</v>
       </c>
       <c r="C309" s="36">
-        <v>26.460515411108545</v>
+        <v>0</v>
       </c>
       <c r="D309" s="36">
-        <v>51.633333333333333</v>
+        <v>19.266666666666666</v>
       </c>
     </row>
     <row r="310" spans="1:4">
       <c r="A310" s="29">
-        <v>80101</v>
+        <v>40301</v>
       </c>
       <c r="B310" s="30" t="s">
-        <v>320</v>
+        <v>179</v>
       </c>
       <c r="C310" s="36">
-        <v>77.81096324444259</v>
+        <v>0</v>
       </c>
       <c r="D310" s="36">
-        <v>116.3</v>
+        <v>13.033333333333333</v>
       </c>
     </row>
     <row r="311" spans="1:4">
       <c r="A311" s="29">
-        <v>80102</v>
+        <v>40302</v>
       </c>
       <c r="B311" s="30" t="s">
-        <v>306</v>
+        <v>180</v>
       </c>
       <c r="C311" s="36">
-        <v>51.382930652510332</v>
+        <v>0</v>
       </c>
       <c r="D311" s="36">
-        <v>32.966666666666669</v>
+        <v>68.466666666666669</v>
       </c>
     </row>
     <row r="312" spans="1:4">
       <c r="A312" s="29">
-        <v>80201</v>
+        <v>40502</v>
       </c>
       <c r="B312" s="30" t="s">
-        <v>321</v>
+        <v>184</v>
       </c>
       <c r="C312" s="36">
-        <v>68.313444828510441</v>
+        <v>0</v>
       </c>
       <c r="D312" s="36">
-        <v>115.96666666666665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313" s="29">
-        <v>80202</v>
+        <v>40503</v>
       </c>
       <c r="B313" s="30" t="s">
-        <v>540</v>
+        <v>185</v>
       </c>
       <c r="C313" s="36">
-        <v>64.459058153270021</v>
+        <v>0</v>
       </c>
       <c r="D313" s="36">
-        <v>114.56666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314" s="29">
-        <v>80301</v>
+        <v>40504</v>
       </c>
       <c r="B314" s="30" t="s">
-        <v>323</v>
+        <v>510</v>
       </c>
       <c r="C314" s="36">
-        <v>23.242507079703188</v>
+        <v>0</v>
       </c>
       <c r="D314" s="36">
-        <v>39.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315" spans="1:4">
       <c r="A315" s="29">
-        <v>80302</v>
+        <v>40505</v>
       </c>
       <c r="B315" s="30" t="s">
-        <v>324</v>
+        <v>187</v>
       </c>
       <c r="C315" s="36">
-        <v>91.997351102654605</v>
+        <v>0</v>
       </c>
       <c r="D315" s="36">
-        <v>105.63333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316" spans="1:4">
       <c r="A316" s="29">
-        <v>80303</v>
+        <v>40603</v>
       </c>
       <c r="B316" s="30" t="s">
-        <v>325</v>
+        <v>190</v>
       </c>
       <c r="C316" s="36">
-        <v>17.89034991713255</v>
+        <v>0</v>
       </c>
       <c r="D316" s="36">
-        <v>31.866666666666664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:4">
       <c r="A317" s="29">
-        <v>80304</v>
+        <v>40802</v>
       </c>
       <c r="B317" s="30" t="s">
-        <v>541</v>
+        <v>194</v>
       </c>
       <c r="C317" s="36">
-        <v>74.146815154014405</v>
+        <v>0</v>
       </c>
       <c r="D317" s="36">
-        <v>97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:4">
       <c r="A318" s="29">
-        <v>80401</v>
+        <v>40901</v>
       </c>
       <c r="B318" s="30" t="s">
-        <v>327</v>
+        <v>195</v>
       </c>
       <c r="C318" s="36">
-        <v>37.310163037142893</v>
+        <v>0</v>
       </c>
       <c r="D318" s="36">
-        <v>23.400000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" s="29">
-        <v>80402</v>
+        <v>40902</v>
       </c>
       <c r="B319" s="30" t="s">
-        <v>328</v>
+        <v>196</v>
       </c>
       <c r="C319" s="36">
-        <v>6.9357747260368994</v>
+        <v>0</v>
       </c>
       <c r="D319" s="36">
         <v>0</v>
@@ -45040,80 +45040,80 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320" s="29">
-        <v>80501</v>
+        <v>40903</v>
       </c>
       <c r="B320" s="30" t="s">
-        <v>329</v>
+        <v>197</v>
       </c>
       <c r="C320" s="36">
-        <v>31.568567566214494</v>
+        <v>0</v>
       </c>
       <c r="D320" s="36">
-        <v>59.166666666666664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" s="29">
-        <v>80601</v>
+        <v>41202</v>
       </c>
       <c r="B321" s="30" t="s">
-        <v>330</v>
+        <v>513</v>
       </c>
       <c r="C321" s="36">
-        <v>13.468013468013467</v>
+        <v>0</v>
       </c>
       <c r="D321" s="36">
-        <v>11.4</v>
+        <v>44.766666666666673</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" s="29">
-        <v>80602</v>
+        <v>41301</v>
       </c>
       <c r="B322" s="30" t="s">
-        <v>331</v>
+        <v>202</v>
       </c>
       <c r="C322" s="36">
-        <v>33.555737886852107</v>
+        <v>0</v>
       </c>
       <c r="D322" s="36">
-        <v>36.966666666666669</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" s="29">
-        <v>80701</v>
+        <v>41501</v>
       </c>
       <c r="B323" s="30" t="s">
-        <v>332</v>
+        <v>204</v>
       </c>
       <c r="C323" s="36">
-        <v>37.456664355715738</v>
+        <v>0</v>
       </c>
       <c r="D323" s="36">
-        <v>49.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" s="29">
-        <v>80702</v>
+        <v>41502</v>
       </c>
       <c r="B324" s="30" t="s">
-        <v>307</v>
+        <v>515</v>
       </c>
       <c r="C324" s="36">
-        <v>34.16648480285405</v>
+        <v>0</v>
       </c>
       <c r="D324" s="36">
-        <v>50.066666666666663</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" s="29">
-        <v>80703</v>
+        <v>41503</v>
       </c>
       <c r="B325" s="30" t="s">
-        <v>333</v>
+        <v>206</v>
       </c>
       <c r="C325" s="36">
         <v>0</v>
@@ -45124,52 +45124,52 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" s="29">
-        <v>80801</v>
+        <v>50405</v>
       </c>
       <c r="B326" s="30" t="s">
-        <v>334</v>
+        <v>250</v>
       </c>
       <c r="C326" s="36">
-        <v>9.0130899448678203</v>
+        <v>0</v>
       </c>
       <c r="D326" s="36">
-        <v>27.333333333333332</v>
+        <v>3.0333333333333332</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" s="29">
-        <v>80802</v>
+        <v>50501</v>
       </c>
       <c r="B327" s="30" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="C327" s="36">
         <v>0</v>
       </c>
       <c r="D327" s="36">
-        <v>18.600000000000001</v>
+        <v>4.333333333333333</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" s="29">
-        <v>80803</v>
+        <v>51001</v>
       </c>
       <c r="B328" s="30" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="C328" s="36">
         <v>0</v>
       </c>
       <c r="D328" s="36">
-        <v>8.0333333333333332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" s="29">
-        <v>80901</v>
+        <v>51003</v>
       </c>
       <c r="B329" s="30" t="s">
-        <v>543</v>
+        <v>524</v>
       </c>
       <c r="C329" s="36">
         <v>0</v>
@@ -45180,212 +45180,212 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" s="29">
-        <v>90101</v>
+        <v>51101</v>
       </c>
       <c r="B330" s="30" t="s">
-        <v>544</v>
+        <v>237</v>
       </c>
       <c r="C330" s="36">
-        <v>97.011032640562973</v>
+        <v>0</v>
       </c>
       <c r="D330" s="36">
-        <v>91.566666666666677</v>
+        <v>8.3666666666666671</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" s="29">
-        <v>90102</v>
+        <v>51302</v>
       </c>
       <c r="B331" s="30" t="s">
-        <v>545</v>
+        <v>244</v>
       </c>
       <c r="C331" s="36">
         <v>0</v>
       </c>
       <c r="D331" s="36">
-        <v>55.733333333333327</v>
+        <v>11.866666666666667</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" s="29">
-        <v>90103</v>
+        <v>51501</v>
       </c>
       <c r="B332" s="30" t="s">
-        <v>546</v>
+        <v>247</v>
       </c>
       <c r="C332" s="36">
         <v>0</v>
       </c>
       <c r="D332" s="36">
-        <v>23.633333333333336</v>
+        <v>29.433333333333334</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" s="29">
-        <v>90104</v>
+        <v>51601</v>
       </c>
       <c r="B333" s="30" t="s">
-        <v>547</v>
+        <v>248</v>
       </c>
       <c r="C333" s="36">
         <v>0</v>
       </c>
       <c r="D333" s="36">
-        <v>46.633333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" s="29">
-        <v>90201</v>
+        <v>70802</v>
       </c>
       <c r="B334" s="30" t="s">
-        <v>548</v>
+        <v>292</v>
       </c>
       <c r="C334" s="36">
-        <v>62.334971357668138</v>
+        <v>0</v>
       </c>
       <c r="D334" s="36">
-        <v>33.93333333333333</v>
+        <v>21.433333333333334</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" s="29">
-        <v>90202</v>
+        <v>70803</v>
       </c>
       <c r="B335" s="30" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C335" s="36">
-        <v>7.5159714393085304</v>
+        <v>0</v>
       </c>
       <c r="D335" s="36">
-        <v>18.966666666666665</v>
+        <v>13</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" s="29">
-        <v>90203</v>
+        <v>70805</v>
       </c>
       <c r="B336" s="30" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="C336" s="36">
-        <v>67.505794184080472</v>
+        <v>0</v>
       </c>
       <c r="D336" s="36">
-        <v>24.066666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:5">
       <c r="A337" s="29">
-        <v>90301</v>
+        <v>80703</v>
       </c>
       <c r="B337" s="30" t="s">
-        <v>550</v>
+        <v>333</v>
       </c>
       <c r="C337" s="36">
-        <v>53.59056806002144</v>
+        <v>0</v>
       </c>
       <c r="D337" s="36">
-        <v>27.366666666666664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:5">
       <c r="A338" s="29">
-        <v>90302</v>
+        <v>80802</v>
       </c>
       <c r="B338" s="30" t="s">
-        <v>260</v>
+        <v>335</v>
       </c>
       <c r="C338" s="36">
-        <v>58.578743315801695</v>
+        <v>0</v>
       </c>
       <c r="D338" s="36">
-        <v>17.566666666666666</v>
+        <v>18.600000000000001</v>
       </c>
     </row>
     <row r="339" spans="1:5">
       <c r="A339" s="29">
-        <v>90303</v>
+        <v>80803</v>
       </c>
       <c r="B339" s="30" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="C339" s="36">
-        <v>69.138269149000891</v>
+        <v>0</v>
       </c>
       <c r="D339" s="36">
-        <v>100.26666666666667</v>
+        <v>8.0333333333333332</v>
       </c>
     </row>
     <row r="340" spans="1:5">
       <c r="A340" s="29">
-        <v>90401</v>
+        <v>80901</v>
       </c>
       <c r="B340" s="30" t="s">
-        <v>325</v>
+        <v>543</v>
       </c>
       <c r="C340" s="36">
-        <v>41.753653444676409</v>
+        <v>0</v>
       </c>
       <c r="D340" s="36">
-        <v>108.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:5">
       <c r="A341" s="29">
-        <v>90402</v>
+        <v>90102</v>
       </c>
       <c r="B341" s="30" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C341" s="36">
-        <v>21.753317380900587</v>
+        <v>0</v>
       </c>
       <c r="D341" s="36">
-        <v>38.766666666666666</v>
+        <v>55.733333333333327</v>
       </c>
     </row>
     <row r="342" spans="1:5">
       <c r="A342" s="29">
-        <v>90501</v>
+        <v>90103</v>
       </c>
       <c r="B342" s="30" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="C342" s="36">
-        <v>80.820709488359839</v>
+        <v>0</v>
       </c>
       <c r="D342" s="36">
-        <v>106.90000000000002</v>
+        <v>23.633333333333336</v>
       </c>
     </row>
     <row r="343" spans="1:5">
       <c r="A343" s="29">
-        <v>90502</v>
+        <v>90104</v>
       </c>
       <c r="B343" s="30" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="C343" s="36">
         <v>0</v>
       </c>
       <c r="D343" s="36">
-        <v>10.5</v>
+        <v>46.633333333333333</v>
       </c>
     </row>
     <row r="344" spans="1:5">
       <c r="A344" s="29">
-        <v>90503</v>
+        <v>90502</v>
       </c>
       <c r="B344" s="30" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C344" s="36">
-        <v>39.424403705893951</v>
+        <v>0</v>
       </c>
       <c r="D344" s="36">
-        <v>12.366666666666667</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -45398,6 +45398,9 @@
       <c r="E349" s="31"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D349">
+    <sortCondition descending="1" ref="C1:C349"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -50654,22 +50657,22 @@
         <v>0</v>
       </c>
       <c r="D2" s="30">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E2" s="30">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="F2" s="30">
-        <v>36.700000000000003</v>
+        <v>42.5</v>
       </c>
       <c r="G2" s="30">
-        <v>36.700000000000003</v>
+        <v>42.5</v>
       </c>
       <c r="H2" s="30">
-        <v>56.8</v>
+        <v>75</v>
       </c>
       <c r="I2" s="30">
-        <v>56.8</v>
+        <v>75</v>
       </c>
       <c r="J2" s="30">
         <v>433.4</v>
